--- a/data/google_news_dedup_15_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_15_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,32 +480,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brand Protest</t>
+          <t>BV Value Retail Crime (fallback)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi") AND ("protest" OR "animal rights" OR "fur free" OR "PETA" OR "activist") AND -BAFTA AND -"red carpet" AND -"awards" AND -"wears" AND -"dressed in"</t>
+          <t>("Bicester Village")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Armani Effect - 10magazine.com</t>
+          <t>Does Lululemon’s clothing contain ‘forever chemicals’? - Firstpost</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Armani Effect - 10magazine.com</t>
+          <t>Does Lululemon’s clothing contain ‘forever chemicals’? - Firstpost</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 11:30:30 GMT</t>
+          <t>Wed, 15 Apr 2026 10:24:25 GMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE51UjZkeHdPNklPVlVqMGdNeGVJLS1JX2ZUenVMV0p4blFtdmVhMDMtd3BfcVA1SlRzU1pyQlBqREYxRTNJVzJtYkhTSnB2WUFPblJ2Z1BkNFM2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNT1hKbGQxNC1jend2Mm9xaEpoSmVIX3JxQ0NDNGdIdUZxb1lfXzhfQlJseEJLTHg0VFpqNkNZQ19YQ0sta3Nld0VVNE43bWxmbGljbGktWFlZUnlFanlNRkpUOXFiMU9TN2hsckJjSkVPczVkRWN0aVZ1NGtHUU50MlpLSzMzaEJ5OE5Xd2xGaHk4X3FUZWx6SFNtVWN6R1FXTndIMjN30gGmAUFVX3lxTE1PWEpsZDE0LWN6d3Yyb3FoSmhKZUhfcnFDQ0M0Z0h1RnFvWV9fOF9CUmx4QktMeDRUWmo2Q1lDX1hDSy1rc2V3RVU0TjdtbGZsaWNsaS1YWVlSeUVqeU1GSlQ5cWIxT1M3aGxyQmNKRU9zNWRFY3RpVnU0a0dRTnQyWktLMzNoQnk4Tld3bEZoeThfcVRlbHpIU21VY3pHUVdOd0gyM3c?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,38 +529,38 @@
         </is>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46126.47951388889</v>
+        <v>46127.43362268519</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brand Protest</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi") AND ("protest" OR "animal rights" OR "fur free" OR "PETA" OR "activist") AND -BAFTA AND -"red carpet" AND -"awards" AND -"wears" AND -"dressed in"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIKE THIS MY BE GENUIS! BUT WHO WINS NIKE OR SNEAKERHEAD? [de8c81] - Fathom Journal</t>
+          <t>Evri speaks out as delivery firm shuts with drivers fired - Oxford Mail</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NIKE THIS MY BE GENUIS! BUT WHO WINS NIKE OR SNEAKERHEAD? [de8c81] - Fathom Journal</t>
+          <t>Evri speaks out as delivery firm shuts with drivers fired - Oxford Mail</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:53:53 GMT</t>
+          <t>Wed, 15 Apr 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5sOHdKT0N6WWVVM1FoYnE1SEFWUXp4MEFXRE9PRm1sYmhCS2hMUWp0cGNEVEo1UXd1OWhvRzhKZ3RyOE50YU1ocjJpcmhrYlktMk1MZ25DVFVvMEVVaDhQQW5rWEhlRFVUMFE0SEF4bFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNQ3NQTDV0WUZzV1o4UUVkMjVSc1RWSXNnZDdGLVpPYlZpcktnWGVyMmg1M2tkSGxXYkNEbUx6RXhTUV93WGVZd25KZW1NVEx1UzFGYkM5LVVwU0JDaDdBV3FES01OYmpKQmg5aWRYOHZWWGdhTW9BQkx0NndjQkZYUHhrcFA5U19HZnVjYjhhMnZYRU1mNHRlUXJOQQ?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -584,38 +584,38 @@
         </is>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46126.66241898148</v>
+        <v>46127.41666666666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bicester underpass plans 'genuine victory' for campaigners - BBC</t>
+          <t>Council to write to Royal Mail over delivery delays – allegation “mail was concealed by management from local MP” on a visit - Wrexham.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bicester underpass plans 'genuine victory' for campaigners - BBC</t>
+          <t>Council to write to Royal Mail over delivery delays – allegation “mail was concealed by management from local MP” on a visit - Wrexham.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 11:58:50 GMT</t>
+          <t>Wed, 15 Apr 2026 07:45:28 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9xMVpKbUM2b0UyUFZ6OE5sSkV4Y3JuamdrRHlLbzBDS1hrS3FORXN5c3pwcmlnU0N5bzBHVFZqSEc2d3RoaU5jY09qMy12R1J4Q2VBVjNvN2YxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxObHd6NFZsQTZKLUtiLVJHbE9ZZTVIekx2XzRGOXdhb2JFbkZpSHcxYm9Dek5saTdTcExoUkRSOVNwZUdkYjNpdWVqcEZRUGgydWFINzB3Y2hJMGRLMlJPcXRFMDc5ejNlRnV5TjZPdGVkU1V1aGptWW1HWjZsZ2MwTktWRVg1QzdfUHVmVXU1c2h5cTVwZ1pVTzFZVmVyRExuR0YwNjRZejlyYzFaNDBSWElRd1ZDSVh4UnJ3M2FXcndJR19RcDgxYjU2VW92Ti02bTZhemQ4ejBuNl93aklPM2dKZEZGUl9GaTU5ZFVR?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,38 +639,38 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46126.49918981481</v>
+        <v>46127.32324074074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Clarion, 14 April 2026 (the Morris edition) - Oxford Clarion</t>
+          <t>Royal Mail delivery disruption hits 34 UK postcodes today as delays continue — full list - The Mirror</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Clarion, 14 April 2026 (the Morris edition) - Oxford Clarion</t>
+          <t>Royal Mail delivery disruption hits 34 UK postcodes today as delays continue — full list - The Mirror</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 10:14:17 GMT</t>
+          <t>Wed, 15 Apr 2026 08:07:00 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4yY2w1ZlpTN3pOcGJLMkJSdW9iUzd0YnZ6MEdWMTNQRDdUNEd4SEZVWG9MbC1FeHpzbVktcGZvNVZMZkdNenFqVVpHNTZQa09LSV9ETkhJa2VSb1RKdTl2RGNMUlhBVVZMMEtWdG4ybmhMWjhxREpYdG5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOTFNIdlZ6a2x0cVdEajJROXRyMXljOEFCMUhRelExOTRvSDdQX29IeUxId25ZajEyTmdEaVhzVGRtNUpKY2hSQ0k3Y0hvSXdLZWkzcEhHenoyM013WFZiaXFfRXhBU2czRWg0YVlfOTBRTTkydVRCTF9RUzh1VkJyMVRXcXdOa1hQX0hUS3lSQm9ValnSAZgBQVVfeXFMUE00LUIwVzR2RjF0bFd5OUI1WTBNXzZmc2JhWGY1dWVUX1hNc18xTFpKMjMzRHJYUEdYdm5zcW1pMFRXSU1KRDJiRXd5cEpFQWt1QVdfeGxhZ3R3enl3MWxRQnU4MGRxc2VaVUZIcGlYcGpULWFEdHNBUzZ3RDdDMGR4UlJHV0o0el9SU3BTbm9FRUg3MWZETjQ?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46126.42658564815</v>
+        <v>46127.33819444444</v>
       </c>
     </row>
     <row r="6">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Target takes on Amazon and finds a partner for its next-day delivery program - The Independent</t>
+          <t>Italmark teams up with Amazon for grocery delivery - Vertical Farm Daily</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Target takes on Amazon and finds a partner for its next-day delivery program - The Independent</t>
+          <t>Italmark teams up with Amazon for grocery delivery - Vertical Farm Daily</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:03:00 GMT</t>
+          <t>Wed, 15 Apr 2026 12:10:04 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQYzBLRTQ2MnN1MHBuNzY4bDUtMUtwYkdtTlRTNFJWU0oxSEFTNEYyY1BNNVB1MGQ5MXNMMksxaTlvd2NGbFlSTkFwekZJNDN0TlIyT1NZdzRJek5YbHNfNDFTY3gwWUxPRGIwY0dSWTQ3a3BYTExhQ2ZISFF3a0JSSVBDaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNZWZWX1JmMm5qUWFmSWx5eXQ4ckRoN3c5c1ZUdW4yQmVSYzFSOS1OMTAzd0lEQldUYkE1NmRxcl81WUFGaUVwWGVka3l3WFVsU18xT2VIeFlWM0ZWZDlNSUNCVkR0bm9NOHQwODAxNmNBV19tU2tDQ1VNTzVuSnZ2MVZNNE0tN01nNTRlX25ZY3M2eVNuQ2U2dzg0c1c5TWRXUEUw?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46126.62708333333</v>
+        <v>46127.50699074074</v>
       </c>
     </row>
     <row r="7">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hauliers ECM Vehicle Delivery and DHL lead the pack in latest fleet increases, MT Fleet Data reveals - Motor Transport</t>
+          <t>Amazon to sell new weight-loss pill Foundayo via kiosks, home delivery - MSN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hauliers ECM Vehicle Delivery and DHL lead the pack in latest fleet increases, MT Fleet Data reveals - Motor Transport</t>
+          <t>Amazon to sell new weight-loss pill Foundayo via kiosks, home delivery - MSN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 09:18:14 GMT</t>
+          <t>Wed, 15 Apr 2026 08:16:05 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNWDd2YjU5RmtEN0w5UEhYODU1Ri1RNUlwb01qdm5uWTVkUzhFWTluVzVNa2hnMnptbzZVSWsxMHY4RXVaS1h0N0VGQ0E2TVBlUVlpNUZNSndpUnNmT2ZkcTZEajhEN2Jhb3VXUlprakU2SVFKaXpjU0tiUXBJNTJ1WFRham5qdkU4X0FvX3VOcGxmSDFtSGIxb3hfOHlobGx6eXFxUXpEa1pvbnJZdlhySzByb2p2eTdOcDhIT2pKaDRWY0F1SE5aZnpDUDZ2VzVqZlkzM2hSbXpfT2k2cVBybg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVGFKMWN0eEdEMW5EdmFYQndhaGVFWTBnMFdnZ1NzS083VzE3YzFVS2RWQlJNcDFXaE9BeWJNUTVnaVdlcjdpNUhnTkNGTF8zQndYVTB2U1BBSnBrWDJkdlhTU0JCNEZYZ1E2LUZiSTBOYnlSajdRTl9xMkIxdE5JdTBIdkMwbUZ5UUFqczVLOWNTcEJ2cnNtTDBNNDJVMFFveEJtVTFiVGtxRGJ6ODd5S09hOVpYRktQWHhXdQ?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46126.38766203704</v>
+        <v>46127.34450231482</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 8 Oxfordshire postcodes today — full list - Gloucestershire Live</t>
+          <t>Winn-Dixie and Amazon expand grocery delivery to most of Florida - Lakeland Ledger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 8 Oxfordshire postcodes today — full list - Gloucestershire Live</t>
+          <t>Winn-Dixie and Amazon expand grocery delivery to most of Florida - Lakeland Ledger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 09:20:00 GMT</t>
+          <t>Wed, 15 Apr 2026 09:08:00 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSldTc2JMdWlvVDktSTJ6VmV0QnZ0RUx6d212czQydThkNmRqQjh3dFpzblpITzhNQzg2ZWZ3SmlvX0p4YVJQaGRzckoxa2tnT0dlazFiM2dSS0NpdF9FdnFQX1FkVmlXR1Vudy15WTVINjZEUW1WQzhOZU9HLWM2enkyNWEweEdfeU9XNTV0X0JUWnJxWjBHMVFNU0hScXN4blMxRVFSa9IBrAFBVV95cUxQRURXYU9RSEVXQUJSdHNXbWE0bmFoRmJNR2Ruc19MZEtpRWpRaXVqV3hMZzRQeVRSMmN0elo0ZGpyekNwY1diTVZaRWN4V2xlRDZWWEN1WTZYcHJTSDFiMklmWWEyYWxtMnZEcFRPMEY4TDdZWHNvRTZ5MFhDd2Zvc0x0NWlOVlFhRDZrLXFnWFhlcUNHWmFrSDd5cWZIMmRycm4wQmUxeUpEa3dt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQTXdLTldIXzlNcUIxTjY2T1JZVzlIRWZaamZyTU1kUHE4NDYyTVU4U2dIRjFVX1NocURRR09IQ0YzQWZ4eDYzc2hWMGJGeUplY1NCNDlXbW1seTVQMmZmdm9uaXVERG1hbDZpSXhfY2tJcDI2QkJYMkxIN0s3cTJnaUw1V0ExaDYtVDNsYmE4UUxfMFZnak8wUGVud0FYaUVqVk9QcHJ1c19JaWVGb0laUGNSQ1FrZnlKQjJLUHAxNVJ6Qkd1U0YwSUVvVEZGaVFpeUVoeWM2eFptNjdtbFRZMXQ2UQ?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,38 +859,38 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46126.38888888889</v>
+        <v>46127.38055555556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>London Marylebone</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("marylebone station" OR "london Marylebone") AND ("incident" OR "delay" OR "closed" OR "delays" OR "protest" OR "boycott" OR "bomb" OR "Bomb threat" OR "shooting" OR "explosion" OR "stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DHL, IAG Cargo Expand SAF Deal To Cut 640,000 Tonnes CO2e, Secure Long-Term Fuel Supply - ESG News</t>
+          <t>Delays continue at London Marylebone after disruption — what you need to know - London Now</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DHL, IAG Cargo Expand SAF Deal To Cut 640,000 Tonnes CO2e, Secure Long-Term Fuel Supply - ESG News</t>
+          <t>Delays continue at London Marylebone after disruption — what you need to know - London Now</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:55:20 GMT</t>
+          <t>Wed, 15 Apr 2026 07:36:36 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMk5Sak9IUkVMVERETkNhcVBxREY3ekp1bjM1V3hCOElhUGZRSkZBZGV2XzZPenBBTUJkaEd5Qml6MTJBMXkyM1ltb2ZKc1U5ZUMya1VnNklXdTExYUxxejNSSm9CWmtVUFk0aGd4cTNCSlJQTkI5YkE5NDU2aHl5TmtpRm5lY2FKaE53QldlUDJTektNWUN1SzNRUEROWTdZQUl3UFNuSzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYWhwQkpqSEx2b3RzdVhRV1NVTGxPY2lVWDlDV1VYdUhoRTVUYXRRUVN0ckpZbUlabS01a3JHQnp3aWJ1UkRJYUVtdWU1VVdFb1V3WVZUTEJPalE3dGk4SmZDdlNuSk5xejNHdW1BRGh5ZHk2cXRUTHZ3eHdVZklDYXZWejlkR0xVR2FsNTdma2dZbDVGYjE4cUJEZ3E1YzQ?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,38 +914,38 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46126.66342592592</v>
+        <v>46127.31708333334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>London Marylebone</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("marylebone station" OR "london Marylebone") AND ("incident" OR "delay" OR "closed" OR "delays" OR "protest" OR "boycott" OR "bomb" OR "Bomb threat" OR "shooting" OR "explosion" OR "stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>LIVE updates as rush hour London trains hit with MAJOR disruption - London Now</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amazon expands grocery delivery partnership with Winn-Dixie in Florida - Digital Commerce 360</t>
+          <t>LIVE updates as rush hour London trains hit with MAJOR disruption - London Now</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:50:33 GMT</t>
+          <t>Wed, 15 Apr 2026 07:25:21 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdGh6Sk9ldmxwRFFLa3RWRHJGTjRfWVpzRlA5WFhOU2JSSng5QXBDcUZmVE5aT2YyWUEwdWFCZVVTOTdsVlBHSGkxQ0xsMlhpMDNEN1N3bEs3czhiZkkwZHR1V3NDWEd1RG1wZHZIMmQ3eVRoMXFCMjk4MmhBTGhrOXlzTUpTRkNhNDdyMnZtWC1NUjdaTGJHZ9IBngFBVV95cUxQYzYwcTZJRHIxOFctWGd1WUZNOEM2YUlHd1hmQ25TWDRPM1NDamZqOEFPRXJwcTFoal9HZU9NR3ZtWmM5UXdZdVVhLWE3OGk0ME5zTDd2ZldsYy0taHJLZnlrVFV3bldSb28zOVhOVHJYOFduaEF6ZGprUDgxQmh6YVhmSzZ2TnNrQ3hYVlJwNjRlVEtIdk5lRjliUUZYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOdUJNSlVucWlsT05JQ0JvYmhNVUFNVnR6ODZ0cU1nSE9XQlhCdlpUN2pjSzNZQnB3dG0xTDlaYzZBUXBITnFpY1Q4VzhhUnE3Rk9OT3dmR1F5VUFiYWF1aDlfV1A2WnFPejduZDZ3OTI1SFBENXpwQ0phcGFlSG1xanNpN3J1UWZlS3EtMzVLRkNOd1U4WVd1SEt6SGxKaV9xVHRRRw?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46126.6184375</v>
+        <v>46127.30927083334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Are Amazon delivery drones spying on you? - The Cool Down</t>
+          <t>Brussel onderzoekt Nutella-maker om mogelijk verboden beperkingen - Welingelichte Kringen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Are Amazon delivery drones spying on you? - The Cool Down</t>
+          <t>Brussels investigates Nutella maker for possible banned restrictions - Well-informed Circles</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 06:00:00 GMT</t>
+          <t>Wed, 15 Apr 2026 12:19:20 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdlpPZjdnemh0S1UwTkIteXlRQnF0MnJsbG5hUEJDaDZLWmVXV2lwZjhpMXdxWEROb3VxUlM1VkhrdGdpWFF6TW5ucU5BZW9sZHpyblFRd1l5MmZrc0N5SzFVc1BtMHlpZVZSNjNhYXpNODBsUHdzaFp0TkFhUG1sc3NJcjlTMEdBM1dxQmo3OFFGU0tPMWJZV1U5bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPbXRfcW1NaW9oNUJzM0J3QUIzYXNVZFl2eS1vSzJlWDVBd0ZRTmlEbUQ5MnlIWGFrS3ZSRnNVWVhHMTRIaEJLVGFWWDFHR1ZqLVcxYThpU3FBZk5oeWpPVjhucW1HUTZ5UEx6QWFHd1lpZVM4dmdOeHBFd18tY2p4Tm9vSFhDcFJhMWpOM0VZanpZelZadFZDTkxPZ3k5bkhJcGRlUk5sSkhMZkJWdmtn?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1010,52 +1010,52 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46127.25</v>
+        <v>46127.51342592593</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon, US Postal Service reach delivery deal - AOL.com</t>
+          <t>Dronebeelden explosie Roermond - De Limburger</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Amazon, US Postal Service reach delivery deal - AOL.com</t>
+          <t>Drone images of explosion Roermond - De Limburger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 03:24:00 GMT</t>
+          <t>Wed, 15 Apr 2026 12:25:58 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOQzJjRElCZVJWS2NkcHNTNG51VVNZZFVyRmt1WnI0RGhpTXEwT0dLRGtvZXppa21tOHRHa281dkpTYVp5ZXpRUnNGZzkyZFZxNmdlY3BiU1BYUmZIakdLV0FpeHNJbkFCbHNwRmFnUl85bGx6Skc1OHpFSktSTGFDLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPcElwNVBHdS1ScUtBY0RJOFNmcjRXbm9VMWJRSFNWN3BaTnRLaW5iVWlBYkFCYURJTW5iQTh1b2lQaDhFQ05fVUJ3eUE2eldsRGFuT1J1MXAxVm1fNjB6bmE5MV9jNkhrNGJWMXhFU3dic1N4UHNOUEhURC1EdG01S2I3WGdTS016ZGc?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,52 +1065,52 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46127.14166666667</v>
+        <v>46127.51803240741</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI-Accelerated Delivery Systems - Trend Hunter</t>
+          <t>Schermutseling ligt aan de basis van schietpartij in Battelsesteenweg: verdachten blijven aangehouden - GVA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI-Accelerated Delivery Systems - Trend Hunter</t>
+          <t>Skirmish is the basis of shooting in Battelsesteenweg: suspects remain arrested - GVA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 21:21:59 GMT</t>
+          <t>Wed, 15 Apr 2026 06:53:41 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBWY1BlTDJ3VFhkc2xxUWZDM0tKc1BWZ3RncXdxQ3NvWTlJZF9ZOFlOdVVfUkpMQWhzWFcyREtHZnYtQThrblFiNTJNRGZYMnN2RG9NamoxdVNUblXSAVtBVV95cUxQVmNQZUwyd1RYZHNscVFmQzNLSnNQVmd0Z3F3cUNzb1k5SWRfWThZTnVVX1JKTEFoc1hXMkRLR2Z2LUE4a25RYjUyTURmWDJzdkRvTWpqMXVTVG5V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOUDhPaFRQQ09NWmNrak9lY0VIUUliOG12dC1FMHo5Uk9RaFZoUVBNRWVLbVlGeHpRSDNjRUxmT0FVY2JRUi00Ri1VM0tqUW5yQkgxV282VzBvaGtUem43b0NRQ0RTb3NMbzRUMmd5RGhESnRtX1BwRDBJQ25nQmdFNVdETHE5akxNNlk1d1JxZjMwaWl3eUdfZ0xaY3FraER1WGNfNnNCWjFSM3dnV1hPN1ZnaGdCcUZXWEVJdnFIOFFXUGxjZkRBMWtYRUowdUdqV2pBdTROU2E0dndrVGxFaUdOUkFZZU14UnlldWZHdElFejlUcUhPT3dpQWVkbTRvcUE?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,52 +1120,52 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46126.89026620371</v>
+        <v>46127.28728009259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FedEx launches same-day delivery with OneRail as Amazon, Walmart boost their speeds - MSN</t>
+          <t>Explosie verwoest woning in Roermond - De Limburger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FedEx launches same-day delivery with OneRail as Amazon, Walmart boost their speeds - MSN</t>
+          <t>Explosion destroys house in Roermond - De Limburger</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 23:49:59 GMT</t>
+          <t>Wed, 15 Apr 2026 10:24:00 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AJBVV95cUxQeWdjMXYtNGhkNTRraWpnTXdEUG8zUENzV2gyRFlzSXlvcTMyT044bUxlX0R1Um0ycXMyMWhNaFpFX1ItLTFkcFNHOEJES0NvMGl3ZmdacHl2OEltVENPaGV5ZC1VZWR3VEFEMkllWF9ZUjNxekpKRjU3cDBoTWFNZ201T21lT29qaG9wamVBVVJKekw5cllSZGpWVEtTVjRFbTBHeFAySnN3M2paTXJNQmc4ckYwR2djblhRdm5EQmRHX0NCR08tenNfVWxpT3RSaFpaVEg2SnIteXZ5cE9rLTU5VlJzS2xpTlNaUEJkSmdzLTZoeUJGUmRMUXY0RE96NEJIOWRrOVBBWGQ5aXpubkc3SnZOdm5ZWTFza1I5VXNnNEhwLS12RVptYzZtSy03V2JtdjVMdW9LdDNQNjU4MTFqOE5UVkJGNFdLbUVMUUlHRkVDSkFBM09GZzVlNTc4aWNsaDZYd1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQSkQxb0lyNzBjTzE5OXcwZGF1N0p3R1VRbWlJMTA4aU1qamhHME1kVjlGaGpQMGNVcVBFV0lZMmVaTTh6blFCS0FlampqRVoxZG1ubWRJY2xVV3V4M3RLeDVDRlpKZEsxMlUzaFZCbUZtS0QydVFqb3NobXFGQzNwS0FYbGozYU8wTDl2VFZqd3Vidw?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1175,52 +1175,52 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46126.99304398148</v>
+        <v>46127.43333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NYC bill would force Amazon to hire thousands of local delivery workers — sending customer bills soaring - AOL.com</t>
+          <t>Vier doden en twintig gewonden bij schietpartij in Turkse basisschool - Nieuwsblad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NYC bill would force Amazon to hire thousands of local delivery workers — sending customer bills soaring - AOL.com</t>
+          <t>Four dead and twenty injured in shooting at Turkish primary school - Nieuwsblad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 00:53:47 GMT</t>
+          <t>Wed, 15 Apr 2026 11:50:32 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE45MUZsTXRnZlFSeFVORWRxVkFHdWZoOEQtSm5DMmJFQUItRnpQUS1SUjNDaDJxaEZQeWN1Y1kwVy02R2lJLURicFRucnI5WWxpVVlCWnpZV3lfbGhuYV95VURXN2lwbFlxVEM5UlBqdnpXcmVjMDEtWHJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTVJyaWEwR0FaMEo3YVliaVBQQmFXTGJ3T0hMaGZvOXBCNVJJRGxVUHdZSG9MTzA2ODRTRWV1MGZXMFBqbEVmcTdScnZBWW5SendNUnVCeGVJN3VPVFJUT1lGYVVVSUV5b3JZYzZKMW5QbGhGZDN5dWtRUVNXVWlhdkM5SjVmemF4T1pqMVFPbTFlU0NxaURPMFAzazVmZzZ3SFNIcmowTE1xMVo3bUhGS1FMRjJ6LTY2ZkJpcFhGT3ZpbjlOaHQtVHJ4Yw?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,52 +1230,52 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46127.03734953704</v>
+        <v>46127.49342592592</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Relief for hotels as Govt ups LPG supply - MSN</t>
+          <t>Nieuwe schietpartij op school in Turkije - HLN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Relief for hotels as Govt ups LPG supply - MSN</t>
+          <t>New school shooting in Turkey - HLN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 02:57:59 GMT</t>
+          <t>Wed, 15 Apr 2026 12:24:30 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOa245c1huU3luNzdiMjNscVA3dzhrbEhtZmIwdnVFbXJ3SFRNNzFlZEhWZFppLXAwRHNKQ0FhUW9OeV9HTWpNUHZJTTN4bmlSU2tQZGNFTUg0Y1YwUU1pSmJHcVNaZHM0NEM0dEltR2RoSEh0YTB1UGx2T1Azc2gxcHh3VnZseDMyMzJxSVVDUy0xZXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPRHlFRUhPY2lpZVByRkFHTGw3S1p3X1lsbl96NmhhTzBZMV9TeXVXR1pHMEZpck5reXVtQzZEVkhZTlRpakRkdmt1SGRNRVBZU1hNaDh5TlRwUlI4eXZhaEt3REM3QWlEajlZcG8wTW5Tcnp1LXNmcTZiVzl1UmQwMGlUamNxYkFiSUljNVpR?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1285,52 +1285,52 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46127.12359953704</v>
+        <v>46127.51701388889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Killer FedEx driver’s chilling searches about his delivery truck after murdering 7-year-old Athena Strand revealed - New York Post</t>
+          <t>Polish MP unfurls Israeli flag with swastika in parliament - Brussels Signal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Killer FedEx driver’s chilling searches about his delivery truck after murdering 7-year-old Athena Strand revealed - New York Post</t>
+          <t>Polish MP unfurls Israeli flag with swastika in parliament - Brussels Signal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 20:02:16 GMT</t>
+          <t>Wed, 15 Apr 2026 07:28:25 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOejZvUTM1Q3B5RkhaQmJxLUlRUnNNLWFpakl3MnItUHJ6TXQyRy03TEJGTGJ5ZTlWbFFiN1dzOVRuWjBQWmE5NUpuT1JwSHRrVF9hS0ZhNW9BOWhfNW5NZUVaeFItX2dNZmFFM2xJVEtpWGFhekRMRmFZTmh5MW5hb0pqUmdhbWoxcTI5Z2xRZy1NNHltS1hhWl8wNGYtMl9HQWd0cDZWWVFiSzFpWTdWNHJSd1hrVEdCUll5TmhiV2phX1FEUzBXQ1B2cENybHpCVzNUYU13OW8tUEZTVjd0OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPUGlQU2FucFpESVA4RWpfNTEybmhtbWNlVm5MMm9OcmlFanp5cXZTSVlxa3VEdjdPUG5YSFNYWHd0Q25zUWlZdEN1WE9Mck9pRU9aeEtfR0JkTVJETkQwN052Uk9OOTBZNW5NSUVsWjQzVlJCVVRWVGxNMzF3ZUpPRncyX0hCcUViQktLSzVFdEZQOXBEVnNVNA?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1345,47 +1345,47 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46126.83490740741</v>
+        <v>46127.31140046296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Le chanteur Patrick Bruel au cœur d’une enquête judiciaire en Belgique pour agression sexuelle dans les locaux de la RTBF - moustique.be</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Singer Patrick Bruel at the heart of a legal investigation in Belgium for sexual assault on the premises of RTBF - moustique.be</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 11:32:35 GMT</t>
+          <t>Wed, 15 Apr 2026 10:30:00 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wJBVV95cUxPYUk4WFhoaDhIUEwyV0d3V3lWWV9DZEZ2bTRpOEU0STY0YkZEWXN6UXR6OTUwbFVvQVJnUjhoSnJYUzhxZ25iSUhPbUl5TTFyVmZiZ0RNTEw0UTRkWE13WEJfdWRqamFuZ1ppc3ZFa3NrM2hQS2IwUWhPVlFBMTNaUWNDblNzamF4c3RYMkFaaHNQaUZsZk1lTGVsMFRRZDk3b3pHZ01oemF6bzJkTWRNZGtCdWhDX0V3Xy1NTVRBT3ExaEVxRWZEX0p1Y3JuX2hhcjJ3bDM1cGx3TDI2MU94dFl3VTNnSV9pNEg1Z2FYUkNUYVFjR2ZsQXJsQU5QdnlnWW5ZZUlHLVMweU90R1llUFJ4Zk5kLWdHSE9BbUxpTDJpMm5yTEhvamJ1NVhPdGN3a1NMdzU0Y2V2eGk5dXJydHlSYmNEV3E3aEI2a1FwOF9sNzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQV2YxY3ZrTE1welJCN0ZLSUM2bVNuWkxhNmFyMGlZTW9SN3dTSFhucHdvR01VMHRjUUp6SXVDTU44cXJJcEZDeUFFM3pIbG40VnpaVnk1eXIzaHlUNGpjS2hlb2Fsd0tUMmo3bEFDa19YUmdDUGJKa3BacFBqem1zaG1MMC0zeFJzSkN0cFVKS3VBbmNnRDJkSkJUYWV2T2dPbGtpTFhwc2NKbjVLV3lKZ1ZoV3JucnVyT1N6RU11VHQyLS0yMUJMNEJQcWJSc29FbVd0RGxrME9hcUFRVVo1ZnNsZW9VLVBzaWF3bERCcS1uNzZuNGZMbWFfTW94UmlzSFo4NHZ3ZHdNMkJBWlptV29lWlowanZSZFpWVGxQRzh4NWlZelhhanNnQnotdTBwQXBMaWc4UzRSdw?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1395,52 +1395,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46126.48096064815</v>
+        <v>46127.4375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verdachten schietpartij Battelsesteenweg blijven aangehouden: 19-jarige krijgt wel enkelband - GVA</t>
+          <t>EN DIRECT - Patrick Bruel : Au lendemain de l’ouverture d’une enquête en France, une autre enquête j... - jeanmarcmorandini.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Suspects in Battelsesteenweg shooting remain arrested: 19-year-old will receive ankle bracelet - GVA</t>
+          <t>LIVE - Patrick Bruel: The day after the opening of an investigation in France, another investigation... - jeanmarcmorandini.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 05:06:08 GMT</t>
+          <t>Wed, 15 Apr 2026 08:57:43 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNUXF6dkFpd1dCVzYyRFdzR01sMHFlUW1NYnpIOW9ndU82RkRDZWN4SDhtbEdUc19BS291cWdUZERuMEVVVHFsV1NrR21OcnFVNlI1V3dRRGIzbU03RUxIa0czbl9IMnNEaS1lLXpPdzNzTURlOHhERzZha2pMYzBicWtuNkdRTnlwSk1SZnJMTUNtazRvVGFUV19rR01sM2phZGZ1M1BFZ21PQmN0emxIOWlFQWVac0diUFdrRGFVenRtbk5WYlhVQUoxQ0dUUnladkU3aFBET3RjSi1UZFZxTk12VFB0YXRYU0hEY3NyM0ZSQmFUTEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxNMjlaNmdJTk93Nk5HWGtRckh2MmhiakFUUzRqWE1sSEJYSFdyR2Qxcl9oM0VNcFRiZC1oSnlSa25oTUZ0ZWhMdGdLRUJVZ1ZDdWtkMGtSemE3NkFBMVJ2UHpfSkZIY0hPU3BuMU5XYmpGZXg2SG9wLUlsUjZwZGhNY2tOUnF3dDJiZmtIOUpHLXJRa0RhZjFRN0lPdGJ5VEZOYU5pY1c1a3JBMTcyMmJvLTZQejBfVkx5NldDaktxMGU0ekx0ZFBwZERMbHhVSi1QVGNvVmxyUTJEQnZNOU5IRnkyZ2tEb3dMQU5iTUN0azJNWVozWUNPTjhldFVNZUF1enlkanhtbG5UNDJTUWlUQU1mRWFDamdDbUtJaTlJSTZIRVNUakE2bFA3QmU5LVZKVHhLVndPNE1qUGxmZ2xSeWR3elJoLWhtR2N3Ny1WYTVtQmx0SUt3Ml9IelQwMGNXd2ZXQlZzVTVzVUdJbWFsNjAyMFduaVNT0gH-AkFVX3lxTE1OODl0aWJvYmVoam9NU1U0ZTJkMFpBTkowbGVpSzU5aGZHcU8yQ09nWHFMRHRURVVDU0l4UFFIc2llRGJ1S3M5cDZsOHJ5VVVOVFF5TXlLUUhWakozcmtCckp4Zzh1N3BSMGI4OElwdi1RSTNkTkhHX1h0X0VmWGZEaGQ5UkV5b2dFLVE5NjRoR1d4cUJwRWxpczBtRFFlMkpEVE5JcjVkWlBraWR4RXFvZUpiZFZ0enJjbU0ta3FZTnBVN3NqRW4xNlQyUWU0UmVGN1RFREltdmxfV0RNWTM0aEVvMnFjMl9TX2lxSngwRnkwc19Tb3dTSV9iVFpTSm5sUUFqa1VlSVp0cFJXTW9QdE5fVWVGMzdUNkRnYXE4VGR1bDJwQWRSR0FsVlZ1MmhmNnVzWG9OTWp6eG5hZ1ZEQ3Y0LWFYNHdPRFFOX3BjTjU2dVVoYk01RmJUNzhxWUl4S2VOaGtLbE5tRjUwb1VSSXdHVVhRby1PQTFLRXc?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46127.21259259259</v>
+        <v>46127.37341435185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Werknemer raakt gewond bij ontploffing in bedrijf in Deurne: “Na explosie volgde steekvlam” - HLN</t>
+          <t>Flitscamera's draaien overuren: hoeveel bestuurders werden in Maasmechelen al betrapt op te snel rijden? | Foto - HLN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Employee is injured in explosion at company in Deurne: “Flash followed explosion” - HLN</t>
+          <t>Speed ​​cameras are working overtime: how many drivers have already been caught driving too fast in Maasmechelen? | Photo - HLN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 08:59:57 GMT</t>
+          <t>Wed, 15 Apr 2026 11:29:48 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOWDhGYjkxZF9lMVByb1dhNm1neUd3Z010Ql9pRXRmeWJWRmlqeGZpMUNaZWxjSzZYZlZFRjJlbmRCYkk2RVQtYmJYTXhwNTNsc3EtRkpERGUxOUd1UlRKZ2JxVUstdDIzY284RENtSjR1eHFEdThZYUxHMWsyQlAxNVQ0SVRxQVZlX2x4RmdFUmxlVE1EcjVKWFFjY1R5a0RaRF91eHJ2OVpkZ2xZQ3d1MVFUNXEyd0M3RGg2bGN4T1BvR2ZrbUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQWEsyc3FCYzNWTVJ5b3dLOWNBMUJQVkZULTE5NlpwM0RhcVd1c0RoLTVKMHdXdTlIdjQyZkJfTFljd0Nsd0VBZkNpb1VlMXA5dHU3ZlZVRWtPSHlmaVQ5Y0JhSGUzX01hTndVN2FPa09PblVTUnJSRE1tSVRmNV9adHctU2Ytc3RoeW9kRkE0dTh4NkxURlBYZGQwQnRJd1h5bWhiWWxhRktsMWV3cEtmV3pSV2RNaGpiYVNvd1czam9ZQThnczdHT2p1Wm1veldTNUlwS3lCcG5NVGN1cnNkSGlJWjk5LWFx?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,38 +1519,38 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46126.37496527778</v>
+        <v>46127.47902777778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fietser geschept door auto in Maastricht - De Limburger</t>
+          <t>Tiener (14) aangevallen en beroofd door groep jongeren in Lanaken - VRT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cyclist hit by car in Maastricht - De Limburger</t>
+          <t>Teenager (14) attacked and robbed by a group of young people in Lanaken - VRT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 04:53:48 GMT</t>
+          <t>Wed, 15 Apr 2026 12:24:58 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNWlUbVkyWkVyUjdQeUd4M3pPNF93MENzbTNUQ0VaOE5WbmtSU3NuTnlzSWVoUGNnVlVSSEJiT3Rna2RtM3lnLUlBWFZodmhJcHktY1pjNm5jRGlpMzdvZl9yTzZxbWNpLUdpNTRqTUtac050MlZGaGVPd0JHUWpqLUtRQjZfcFNIalJaakVpVmhzWmRSTExVZERqOGgzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOd2dxMTVhdk5RZU0xWXVqTVFOM0tudkR0eDBWQnp4Y1ZhYTE4RElmeGVGaWV0bjZ4bmtfQnU1ZXJjUndCYWlZNVV6bU5iaC1xU0hIZGd5Q3Vzcm1hYWVReng4OUo0OVlEOWVHUW15enlheE4yc3NheGh2bUtOWWwwaElpVmh2d29JNjJQLUpwdXlCOUJ5VFhxRW9GVE5RemxCSEtR?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,38 +1574,38 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46127.20402777778</v>
+        <v>46127.51733796296</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen French (fallback)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parket zet deur op een kier voor vervolging van politiemensen die betrokken waren bij dood van Sourour Abouda (46) - Nieuwsblad</t>
+          <t>À Bilzen, le RSCA Futsal joue pour le leadership et la confiance (15 avril 26) - Anderlecht-online</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Public prosecutor opens the door to prosecution of police officers involved in the death of Sourour Abouda (46) - Nieuwsblad</t>
+          <t>In Bilzen, RSCA Futsal plays for leadership and confidence (April 15, 26) - Anderlecht-online</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 10:42:54 GMT</t>
+          <t>Wed, 15 Apr 2026 07:36:00 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPNUJBRmJib2FmT1puZGFUZFpQUFdNclZoZ2RWMTA1MHUwdC05N24tOUlMa0FLSWhsYUgxV1BSWU00Q0VyS25remVTZmdPdmJMRlZGSWFUS2ROekk0Q3hXRFFfWTNweFdCQzB6ekZrZ28xRnFRcS1xRjZUOFhQc2otRkotaHo1RGJOa1NQeWtkS1R5d2l3cm9udXhLWjRSUTZsRXRWQUp1ek1zYlZLdG1oVWdycS1xMGNzbW8xTWlmaUZjZlBiZnFkdlJ4aUlSRzl4TlhHcWRYdndsNXVnbEdJbEd5LTdTVjRsNlFPVTVzZFU4M3QyU3NOcXZjUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE81RDdud0V4RWpmX2Vua3VEb2xCQ1g2bjgzczFiUDIyN3pVSElMMXVhX2p2eGJXalMxRDl6cVZxUlJXSjZSUFJtR2pqT0tZX0JXTzlNUFZEOEVGUFNXa1Nz?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1625,42 +1625,42 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46126.44645833333</v>
+        <v>46127.31666666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Germany English</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich" OR "Stuttgart" OR "Germany") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror attack" OR protest OR strike OR riot OR "hate crime" OR "antisemitic" OR "vandalism" OR "attack") AND -football AND -soccer AND -Bundesliga AND -Bayern</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>“Dit had veel slechter kunnen aflopen”: kelderbrand in Sint-Gillis na nachtelijke explosie - HLN</t>
+          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>“This could have ended much worse”: cellar fire in Sint-Gillis after nighttime explosion - HLN</t>
+          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 11:29:38 GMT</t>
+          <t>Wed, 15 Apr 2026 07:56:44 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMmR0NkNieElmRjRzcWhvMjF6c2FvRFZaSW0wQk0xalVUS3BwZzJualB5NkNoTHFFVThDYkdlYjBpZVVGdG9kZEE4Rk9iUWo4b1hQczFiYVNqcHZBMVZhN29lZkE5Zl9wWXNBYzR0STZaTmJGTzJrMVJxajE1emJLSXNlT3ItZmMtclRHcFZOOS12azJIeGUwaFBOMmJXMi1KeG1TWWcyc2oybFVtN3NnSUw4MVhWTjFOTjZTT1pFYWMydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNN09aN29MQWVkaXY1dmZJb001UkdEdDlKSlVZZkt6OXM4VVc1Zm00WEc2MGJPWGxNdC1SdTN6RlNGZ3VEM0Q0bElVZl82VDFqeWpvOElwRTVKVXVNYmlPTE5UbnZ1bTQzXzJMNVM3aXc4ZkpnMEhQSDk0MGY3M1k3NDhTbUdJZVNlQmY4YkxmZXRwZzBSVGNLTFdR?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1670,52 +1670,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>DE:en</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46126.47891203704</v>
+        <v>46127.33106481482</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Germany English</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich" OR "Stuttgart" OR "Germany") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror attack" OR protest OR strike OR riot OR "hate crime" OR "antisemitic" OR "vandalism" OR "attack") AND -football AND -soccer AND -Bundesliga AND -Bayern</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europese luchtvaart roept Brussel op tot noodmaatregelen vanwege dreigend kerosinetekort - AD.nl</t>
+          <t>Lufthansa Strike Nightmare Extended Through Friday, More than 2,700 Flights Grounded - Travel Market Report</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>European aviation calls on Brussels for emergency measures due to impending kerosene shortage - AD.nl</t>
+          <t>Lufthansa Strike Nightmare Extended Through Friday, More than 2,700 Flights Grounded - Travel Market Report</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 12:59:00 GMT</t>
+          <t>Wed, 15 Apr 2026 11:07:40 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPZXhqQzlUOWNKblhBZk15SklmOVYyT3Byb3dEZWw1Y2JOSmkyTW5rMFBBSEo0MG10ZWFJWFlYZnlvd2VGRjBTOGV1Ri1zX1lDd25NRHFEMkdKdG1sVktLTExfU3h6alZLM1hSc05jOGZXUkFqQ3dkVGFydDNPZUw3dGdTTmYwUmIwWlpqY3R5bG13SXBEa29KSmU5S1NfelQyeElsVnFqdTBWZURDY2hLTmZXM1RZVFVEQjVuZ2phdnB0amM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNQ1ZGalpzdjFHaE1kUFBicF9HcDhfNVFKaHBiNS00SG5OcHFCekEyZHV5SDltRG1aWTUtMkx5WjNGSlhGZ3plcnFkbzYtZmJxZDJib2hjVlYxVjFGbHVteWJhTHFJNTllN0tLcm81UUJSVTI3MGJEdEcwa1VIZ0l2Y2JYTUlHMzc2SnFNTXVSUTRTZDlxWjZCUDl2UmlWTVV4eFpjeUU0RVJjODhTakFTMzNoQ0ZsRllDQVg3ZHBieW11a3I2U2RjY1hB?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1725,52 +1725,52 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>DE:en</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46126.54097222222</v>
+        <v>46127.46365740741</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nachtelijke explosie verwoest leegstaande woning in Roermond - De Limburger</t>
+          <t>Wertheim Selected by California Redwoods in 2026 PLL College Draft - Brown University Athletics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nocturnal explosion destroys vacant house in Roermond - De Limburger</t>
+          <t>Wertheim Selected by California Redwoods in 2026 PLL College Draft - Brown University Athletics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 05:27:57 GMT</t>
+          <t>Wed, 15 Apr 2026 07:05:49 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVmhTb1M5RVB5ZTJPdmIxZmgxV2kwazUyemNhUVhjV0ZSUFNNWS1Ka1hLQWU4OEdXYmxMS2JaZ2Z6UVhycHdMWjdsenJSOGo0Y2EtdzhRV1VwVWpMQ3RpUVR5WDk5X2NlcGtjRHpVTkRac3BWXzBqS2p3OFYwUk5iRndTQXJ4NUxkdlFGa3BWeUdDUlpraS1UQ3hpclhGOE9hMkcxTHgyQ3JGSGpYaURlTTdJNGludw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNdGlqaVJrN19wNU1FbVVnaF80WTRMSGE1WnNXdV8zY1lTSlY4SkxpZmhNX0g5S3FfZE5NbXk4WWZsZEdxeldOcVRFRkczR3d2ZXBEczdjSExYSmJ2R243UHR2OUE0b3huaHBicVNxOGowQWQ3VDdwa2FDc2MyWXB3ZzNQcVV6YVRiZFVCX3FUTmtkRFVfaWVMWjlRbmlNM242cnVTUm1tVk8xaWpscER0dFNwbVZjaXZLVFE?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,52 +1780,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46127.22774305556</v>
+        <v>46127.29570601852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Explosie Roermond - De Limburger</t>
+          <t>Weltkriegs-Bombe in Neuburg gefunden - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Explosion Roermond - De Limburger</t>
+          <t>World War II bomb found in Neuburg - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 04:29:38 GMT</t>
+          <t>Wed, 15 Apr 2026 11:03:11 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1SdGc4NF9yV2t2aFcwb2FURWZYS0VWZ3lhdGxMeHhFX09XSEdVMFZRdkNEY2xfYmJfZGxCSlF0eFpxYXFZMFhGSXQwQzM0U0w1a0dXQjlSRVAtWUNiM19IbUVyeXB1d3RaeEVQT2hwb1I4a1YwYkFvbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5PQXJ3dlRQMi1XRFduTzhPQmdFOHd0b0dfRnRITHZpRFc4dHdlNk5DM1RfUXl0OWlFSXJld2pfWF9UcnhISVlYaExmRFl0MUNEcHE5ZHlFSmU1aHctNno5OA?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1835,52 +1835,52 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46127.18724537037</v>
+        <v>46127.46054398148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Buurt opgeschrikt door schoten in Sint-Gillis: kogelinslagen in gevel maar geen gewonden - HLN</t>
+          <t>FC Ingolstadt 04 - VfL Osnabrück ai prediction 18.04.2026 3. Liga - Livetipsportal.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Neighborhood startled by shots in Sint-Gillis: bullet hits in facade but no injuries - HLN</t>
+          <t>FC Ingolstadt 04 - VfL Osnabrück ai prediction 18.04.2026 3. Liga - Livetipsportal.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:08:08 GMT</t>
+          <t>Wed, 15 Apr 2026 09:44:46 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcDFVUXQ4Si1tanVqcWN0TTlNalNaYUVCclI2SXh0MGZ1aG83SXFLS2Q2REZQeVdEUHU3MS1FcFZFWlBURzlKdHJ1UzZqSjgtcjJscEtRR3MyT1RwOU9LQVlhWVNmbHEzRWFVSm5fLU9MRmdiMmJBVS00N0djaWlUS2ctOV9OR05HcHpzOXNBQnNqYTcxVnU1NDg3UGRTVDVXeEFrMFIteE1RUUxab1pLYTVYZ2xtZG01Uk1Ud0xwZjFSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcWZ1NHhQRTNxdGRZSUZrSGluU25sbDBYbi1menQ1M3BfUEpBV0UwQkZIZzlHMkFYWkMyMjZ4dHMtSmFQUXZ0TEJUUDdoRmZwUG5uMWgxUE9Zc2FWTC1ESWxVSU5OZGY5UUlBVi1QUlVNb3l3VFZLSXFkU2trS01jYkdOaUMxT01xeDk5OXJqVXo5YUd0MFc1NGdUWGF0SjhPTENKUVR3?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1890,52 +1890,52 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46126.71398148148</v>
+        <v>46127.40608796296</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Spain Spanish</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Madrid" OR "Barcelona") AND ("amenaza de bomba" OR "paquete sospechoso" OR "paquete explosivo" OR "ataque con cuchillo" OR "tiroteo" OR "atentado" OR "operación policial" OR "evacuación" OR "artefacto explosivo") AND -fútbol AND -fichaje AND -Liga AND -transferencia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Voortvluchtige vrouw (45) gearresteerd in Wilrijk: celstraf poging tot moord wordt alsnog uitgevoerd - GVA</t>
+          <t>El tiroteo a plena luz del día en Barcelona, nuevo capítulo de la sangrienta guerra entre clanes serbios - El Debate</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fugitive woman (45) arrested in Wilrijk: prison sentence for attempted murder is still carried out - GVA</t>
+          <t>The shooting in broad daylight in Barcelona, ​​a new chapter in the bloody war between Serbian clans - El Debate</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 00:30:20 GMT</t>
+          <t>Wed, 15 Apr 2026 10:44:09 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNZnJBRFpnN2dISkhxd3J6aEFWYWJUWjQ1bXhjNVdtaGhwR3Qxc0FPRDFaNmFLQzhDcVRlRkF5azlDNFYwd0lCRjZBaHZYa202RkdRQk8weVUtX0dQYmk3YUZvNHdsZFZHNkJWVW9XT2oxM3NMYUNQM1gwRGE4MWZ0aEJHSC04dUQ5cFdJTmg1X1UtU1dxWlljaFA5NlRmXzBhbmVsUW9VaGgtNERPczloUmpBakZSUXFYRGp4RG1NLU5SS0lZWXBHOVBGVzJnbHB3ekFmT2VTVDdnX2wxM0stckhYbjFDYUNyT3VjWTlxOTRTdENkNVk1YXh2VElEaWxXS2VjTTJQME94V090Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQUUFRS01iVzBzbUVBQWpDUjNEaFlZeDVrVlFWMmNrdEZiWjlZWHVneHFoVXBjcHJNN3VDbW9wdjZnQl8wd051T1lMSVRqRzFGcDdXVkVacm5ZXzBhODgxNXMyejY0blhzWUJBRkwxSHhKOUx4UXZnNVJPM2ZSQjBlU1lhU1p1QjBsRFJVblZTV0h0d3pmUjJsS1RMeGpxYzJ4UkhkaVFJemdYd1k3T2d5NlhwUjRYUFRIdWVNSS11RWhfaHdEM210emx1eWgyaFJST0FYTHRObzdNUnhKM01qYWFEQXFHdDZ4dWVYYlFR0gHzAUFVX3lxTE92OEhFNnRpYUZHeGF0SzJjcEoxcV9SWlpPcGpQQ3BPdG81QmM4a0traHdTWEhqWXNJS2JNREh4aUkwemtlWl9yRGt0SHVSSnNJTWxacEdkVG9fdVI3YjNOOE5GTnVfeloxRDhscTExclJaZmZSSzlGVGZmREk3QzVZdUJoNkM3c0NCcnRPM2xrd1R6SXJESFoxNTJOR2wwTHcxYXgxMTgycTU4RHB4akVPQjc1QXNpbXExVHBLbE5fWDhlVk0yYkVBcmtFVGVZNTg0WUl5TDBDUDVyNnhFUktiY1p3djltWGdkNUJzNF9Mck0tcw?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,52 +1945,52 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>es</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46127.02106481481</v>
+        <v>46127.44732638889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zeker zeven gewonden bij schietpartij in Turkse school - GVA</t>
+          <t>Killer guilty of fatal suburban station stabbing – West London - British Transport Police</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>At least seven injured in shooting at Turkish school - GVA</t>
+          <t>Killer guilty of fatal suburban station stabbing – West London - British Transport Police</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 09:00:54 GMT</t>
+          <t>Wed, 15 Apr 2026 12:44:00 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNMVVLQ0o5SEVTaGNMVmxKVjZwcnBWQzNxN1BMOVNJLWZFd3BVUDZyZTBXa2x4dlQ2WjVzcVg2ZVZJUVBjSDdJWTdFSGZNeGIzMHNRS2JxZHBOY1VKdS1kaFhFTklhbEFFRzl6UmJqVklZM01PRWRjd3FtMXc4R1NJV3Q1T3hpWHFFSy1ZZWJUT2NxeEZ2RnFrTUt4ODk2YjJC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY2F3UmwxY0taSHFiM0hXM0xYdnlxLVFUeFlZVjlhOGZVWnZndC1KV2U3c3RkX1BodW9ZSC1JSTBqQXFGaHRKZjZCUF9YMjJuSlV5bTFJU2VuNURvcUc4Z18xaXJPdjVIRVV2dXZPaVdrSTNBMVA5ODZjWU1vazJVSk5xRnNYODZMUm4wbHpBRlFPcE15VVdOM3JMeDMxQUdEck82REx0THE2eTNrdUtIakxIRDE0UkU?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2000,52 +2000,52 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46126.375625</v>
+        <v>46127.53055555555</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vrouw (45) uit Wilrijk met voorwaardelijke celstraf nu toch naar de gevangenis wegens nieuwe feiten | Foto - HLN</t>
+          <t>Two more men charged with Primrose Hill murder - BBC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Woman (45) from Wilrijk with a suspended prison sentence now goes to prison due to new facts | Photo - HLN</t>
+          <t>Two more men charged with Primrose Hill murder - BBC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 07:59:32 GMT</t>
+          <t>Wed, 15 Apr 2026 08:51:51 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQSDVjX2VPTEN3blQ1NzVwdVR6dzVxa0twVFQyN18yOXZDc3RhdnVTUFBHQTFWTG42R2RHZXg0bEVnbFZnbG9kMTFHazhXdmxnVzcxeEhOY3laX0h3dGJ6UVdTSFRYbk1tcWpwclR6bjRPdUJ6SDhIdjg5bXZRX1V4SjZGRWhpU3RuWFF1QlYtYVc2YWU3OFNNdDA1VHUzQWt4N0VWSU5IdlFjT3RyVG1yNDlnY0hRX04yenZHSWhOWUtrbzBHYmkxdXZ1anJqLU5ZNlZuTUhoNGRQck1V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPbzNmR3NkakZDRzJWaWdwWUJrUFN3MlIwZTN1NDV3YjRBT3JBUkVzTlZhT3Y0TFRMRWZkM29lWEUyWDQ1RE55RDJNX2Z6X0RmOFJ6eWNzSm1QUQ?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2055,52 +2055,52 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46126.33300925926</v>
+        <v>46127.36934027778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bijna halve kilo ketamine gevonden in studio in Antwerpen: “Er hing nog poeder op zijn neus” - pzc.nl</t>
+          <t>Moment killer laughs on night bus after stabbing student to death in south London - London Evening Standard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Almost half a kilo of ketamine found in a studio in Antwerp: “There was still powder on his nose” - pzc.nl</t>
+          <t>Moment killer laughs on night bus after stabbing student to death in south London - London Evening Standard</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 08:10:00 GMT</t>
+          <t>Wed, 15 Apr 2026 08:13:35 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNX2tpQkV2TGR3SG9NRHhsR2E4eVM4X1diNWJZN2VvcGFob2Z5M241TGdSODY2cWQ4LXJsUzdYZFdVSE03NU5zMWxKUDN4eUM5OWhCVm9pZzFmRG1CSHNOc0Z3ek9lOHZCUlRkQTdnN1p4c2R2cFFUNWtfay1KUzl1TG5fUjlCWE8wcllsMVFYVDB1STNXa1hxWERqVXF3MWdzMHMtQUhEbnZXeEdSYnA0UXdnM2txVFE2ZjV5TjV5SjZLOW5lNkg4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNVd2Uzd1cmVRWVNYNnF2R0JYaFFaTHRXMHdfSU1WcjhvSDYyVjVnUmdaUXliUWdIbWlCYmdyVnAxTkZjTWxHcWFwTDIwcnBHX2lQTENvbHRhOTl5cHdmdXVYdmQ1aW41QkZPZno2NHdBaXV4QjBHMUg0T1l5VFhVbTdRZ1FNY3hnZGo1TDVGYjNmOG1EMS1YX2E5R3ZGRTJZUXlUOTMxUnN4Z19neWpvWlZTZVZfY3B0MGU1Mk5Dell5d3c?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2110,52 +2110,52 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46126.34027777778</v>
+        <v>46127.34276620371</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand weighs mandatory travel insurance to tackle unpaid medical costs - Travel Tomorrow</t>
+          <t>'Days of protests' set for Dartford Crossing and M25 due to rising fuel costs - London Now</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thailand weighs mandatory travel insurance to tackle unpaid medical costs - Travel Tomorrow</t>
+          <t>'Days of protests' set for Dartford Crossing and M25 due to rising fuel costs - London Now</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:45:43 GMT</t>
+          <t>Wed, 15 Apr 2026 11:35:25 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNa0lhZ2JyUHR0QmJDaWV0U2szREFGa0hmRUNsbDlDNy1qZ3R4TlFDWno3XzB0ZXducWZUOGhYYXRpLVQ0amFQVzNRa2VxaXI0ZUVybmpOZ3RnLTM1VXRJOTZQQVZfTkdIWTd6aEJVT1BQb0ZlczlydEF5OVpSeHRpQUpQOWhPSlFOV0czcUhVRV9iSE1FdjZXdy0xSlRiXy12Z2Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPVHl1dkFrLUl2YU1NU0hGVlNSbFFIVV9fT0tVRDlaWkRTOWpFVUlGdWN5UkJYRzNTR3BSZUl3Tjg4QTViam41SHVISFI4aXVJT1pyNnJYYVhLTTQ5dFhsRExfdWVnUVU1UVRYTnE2R3p1QmRDS3hMb0JuREJUcXVfNXV1dVhOMzdidTF1T1U2c3hMSjduZzI4?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2170,47 +2170,47 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46126.57341435185</v>
+        <v>46127.48292824074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy suspends defence co-operation with Israel amid criticism of wars in Iran and Lebanon - Brussels Signal</t>
+          <t>No arrests as man rushed to hospital after stabbing near busy shopping centre - London Now</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Italy suspends defence co-operation with Israel amid criticism of wars in Iran and Lebanon - Brussels Signal</t>
+          <t>No arrests as man rushed to hospital after stabbing near busy shopping centre - London Now</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:55:30 GMT</t>
+          <t>Wed, 15 Apr 2026 09:04:42 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTjFTb3JXMzl4SDF0dy1OSWRtZTdFMkhlMjhkTFY1LU9kOUN5RnhvTF9QNGVDdjNUUW1LOHhfMWVYbUNGUUdudVhRTDBfbjFhWFRVVjBNSkE5YmFzZ3dsZVIwZV9IMVNDNGFhb3hQblJlN3hvQUsyRDVHRnZFLTRIV09GUHpMcndUMmxLZ1lkQWhINFZkam5nX3J4M0FKNmhBZmZ0WF9QamxjUWpOUlJGWEItMUpDVHpvbEhOU1pLRlY3YTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPQUQwM2gyanBoQnFlUUpBell0ZDQtanQta0xqZnJWY1NPdUNCYjBwSzluWExMMGFTSkViVUFYdGFROXdRSExkc2VfYUdvc2VrbDJOR2hPWUJUdzRrSkVwMmZCN05MbEs3dUJ6eVdvM0JZS3BGbmtzYUxubVdqNTJoRXlHUGtCRjZNZ29sSEdWLUlCWXQzUHRTV1ZDTGdUdFU?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2225,47 +2225,47 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46126.58020833333</v>
+        <v>46127.37826388889</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Un couteau sous la gorge et des coups de bâton: quatre jeunes arrêtés après avoir attaqué des mineurs - BruxellesToday</t>
+          <t>Two men charged with murder of Kent man, 19, in fatal stabbing - London Now</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A knife to the throat and blows with a stick: four young people arrested after attacking minors - BruxellesToday</t>
+          <t>Two men charged with murder of Kent man, 19, in fatal stabbing - London Now</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 06:00:00 GMT</t>
+          <t>Wed, 15 Apr 2026 07:51:33 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5zS0hvZzBLNVVKTU9yZ0o3YXV1Y3hTN2pYSUhJUFVBb2pvZWNFamUtN3BIU1daWnoyaXI2bWIxR1Z3elZMVlB6Y0hGQzg2RHRaZ0Frb1NucndPMjJJRzI1OHdORGNUSnF1RUV1aGZMbnlVNmw5X1NmMWpuWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPSDNseWNLX1hWdWFtYm8ycUZuZGJmR0l3a0QxS2V1eGNqZkYtQlhlaUZwbEhILW5haTZ4TTBOZktBVDVGWXdZVTVCckxCaU9OTk9vYzN1TFJQRTQxUkpVUDZiQXZ2NHZ2VmdtSUU3UlhJYmxTSUl1ZjdObkljZXNSd2YxN3JUOFRlVThxeV83ZU00YWwtaHVfVm5pYVB6U24yZkdaXw?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2275,52 +2275,52 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46127.25</v>
+        <v>46127.32746527778</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Agressé alors qu’il rejoignait sa voiture: un homme blessé lors d’un carjacking à Bruxelles | Foto - 7sur7.be</t>
+          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Attacked while returning to his car: a man injured during a carjacking in Brussels | Photo - 7sur7.be</t>
+          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:20:53 GMT</t>
+          <t>Wed, 15 Apr 2026 08:52:00 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNTVdyMDJjTzRQOGl1VDVvT3VCc3BLallBcEZTa0RvcVBmZ2dnc2NNaldZa1JhY3pHVHpENkM0bXhHeDAzaFNuWW1vTy15V2JGWERqUUdLWGRlY1JjTzVsbng3VXZFcVd1NWV2a0xSa25vcE9BUkhZOHNacER1UURsOHEyM0IwaExNTWx0M0JlSjFMQ1N2cy01UTFMTmhKWmxlUU41NkJCa0lnUHZvSmZiSmJia1B0V0hKUzZXOTZ2VEo5RHdIdmlLMTdTNUt1bjFIN041aQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQZTZ1aU9ULWZDREhGLWtWQUVXNk9mVVN2ek84MkhkUWJDbUhRMzBlZHUxc3lvYThnS1E0X1BUMkhHY0h4Qk5GZnJaeGpKclRJdmJoSGdocEVaQTQ3aFRIdEFMbEdMalVsc0VNaXZUb1VXWEZSc2xqNGxTQ2NfdEpWQXdvWTEzV04zTlgzeWVKYWxGWjNMU2ZGRnhtbUtLdnNwUXYycS1oVlJQV195VTZtRHloX3EwdS11WEdXMEZ5Y1dMNE41VElUc3VwMUhZWFZmb0hXQVRIeFM1aERvbFByWUpZeHVpRzVFdmRwT2ZMUXh0anpFSjBCbXk1aDl2TTAxV2x0a3NSVGEyZlZp?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2330,52 +2330,52 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46126.59783564815</v>
+        <v>46127.36944444444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Le procureur du Roi Moinil met en garde contre le "manque criant" de places en institution pour mineurs délinquants - VRT</t>
+          <t>Coalition in London vows Nakba march despite police rejection - The New Arab</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>King's Prosecutor Moinil warns of the "glaring lack" of places in institutions for juvenile delinquents - VRT</t>
+          <t>Coalition in London vows Nakba march despite police rejection - The New Arab</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 08:42:55 GMT</t>
+          <t>Wed, 15 Apr 2026 09:20:51 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYURxai1nVkZxSk02cU12dllCZXo0YURDUnM1S0dPZFZCTlRpSTVfV1U3Y1hvTU40UjNwdUlmTDBBYlBpWVFrd3VOc1BoY2Zsc2s3ZDUtQjJnQS12WnZoTlFsWU14dGRQTGJlSHkzbTdNQ29CMTA3WW5jNzVnWnV1REk5MjczeF9zdzNMM3cwRGxhQ1dKYXBzX3o0THR1TEFjYjNaOXV4bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQZE9HTkNoM29VMVpoSVU1a1A5X0wxQ25CT2JnYjVnTG9YYmlteUZESjZ2eWFHS0dndE0wQVZwRWpjTlZaNTUyWGd0WUFtNVdyUlZuZEZkZ2RZN0o4RlRBTUZ1YzBvQldTNm1oTFJrVGxPdnhHSlBrMVFfWHE5Q2N5cGRVWTBSR09uc3otblVZdWPSAZYBQVVfeXFMUGhsYjBCd0FQTFkxU0J1U1o4S3pkYXRIbk5lMTJaY0E2NmVhWlk0NGhNQ0pkSVhUalVRdjRELU8zempQVEh6WWJkU3BsRUx1RXpJbVdVbzJPUDBmR0R4ZldRZllTdmlUMEhBMkFJSkxldGdYM3hfbVlYMjg0emdWWC1iZDZpMDNHN2I0TGdoQ0pSOGJkaG5B?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,52 +2385,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46126.36313657407</v>
+        <v>46127.38947916667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Une nouvelle marathon de contrôles de vitesse débute ce mercredi 15 avril - BruxellesToday</t>
+          <t>UK Braced for Three Days of Gridlock as Fuel Protest Poster Goes Viral - DM News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A new marathon of speed checks begins this Wednesday, April 15 - BruxellesToday</t>
+          <t>UK Braced for Three Days of Gridlock as Fuel Protest Poster Goes Viral - DM News</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:47:40 GMT</t>
+          <t>Wed, 15 Apr 2026 07:50:20 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPcTdnR1JnNUptN0dld0VyZTFWcGxYMkVxMTZhUFhHdEhqMUs0Q3NtVVNES0xldHV2MGVqWnA1ZjBSSmx3djB5dmhfVTZ1dWlTZWg0bzI4SU0xS092TzZwQmRqNVA1VC1mZW93Y3luRUF5OFk3ankyOFJFZ00wMElINGVUM3hKT3BUbVMwVDdoeFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSVRvNTNxbk9CQTNzVGtIdWJQdksxN2p5Q3NNNkhBTEdIRHRMTi1haTh2SGhqR1E5S09TWncxZXdJYk9UR2xXeXUxMkdHRk1ER0F5T1RPcXJES1ZSaTdJRHBOYzBIUFlXeC1VM05ScTVYS3VPZmZsZkx4SGtlanRyME9ySGhWa1U3Vk9acFpyeDVRZ2FyMVBF?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2440,52 +2440,52 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46126.74143518518</v>
+        <v>46127.32662037037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Les salles de sport réservées aux femmes connaissent un véritable essor à Bruxelles - Euractiv FR</t>
+          <t>Farmers threaten to 'block the M8' near Glasgow Kingston Bridge in protest over rising fuel prices - Glasgow Live</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sports halls reserved for women are booming in Brussels - Euractiv FR</t>
+          <t>Farmers threaten to 'block the M8' near Glasgow Kingston Bridge in protest over rising fuel prices - Glasgow Live</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 12:36:00 GMT</t>
+          <t>Wed, 15 Apr 2026 09:16:00 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPRktBRXMwVDFpc1cwY1Vidm9lSnEwMUZLV2MtbFBoQVZzd2d4LW5QekI0VnEyLUFuMXg4ZUV0bUlXYklKVWZxUGdKY3BOd3J4UEpaREE4a3pkUEhYYXp2QWFfNmhjRUpZajhmeFBfa21SdFNaVjNMZTJCZWF2RWd4VTJBZV9fUlkxTVBqbjFIX05WLUVTTDhXWFZRakctSFg0SXA2VGE3WTJQaFhxUUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOaDd3dUJrTTRCdmNIakhrSWJYV1d3dmJTSnVzTEE4RW9Fa212VTJsOHZVdkp0WnhqVXJGMjQ0V3FtUmNZQjR5U2xJRnlGYTJhb3hJV3hMVVo2VzRjZWJzYW5JNzEyd1JXVFBHejZ6UFVJQ3NfMzBmenZLdzdGZjdHTThYaUpablJkanhTblNGaUvSAZYBQVVfeXFMUDlvR2w0WUhKZ3JES2VDTWhTbkItTFVNa0VKck9WTkZCQmN6OFUzYnd4VkV3UnJqajBYa0ZnUTZLTVc5eXFPenlQMnFSVG9VTVdEdUZjOFVzTzhvUUZvVUhIdlRFVXBvVW01V1pTR2prbWRiU0RtSUllMmJjWGV5OHEwQ0dhWnlGdjVjSzYzWXBOTGU4QUt3?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2495,52 +2495,52 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46126.525</v>
+        <v>46127.38611111111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Patrick Bruel accusé de violences sexuelles: le chanteur visé par une nouvelle enquête pour tentative de viol - 7sur7.be</t>
+          <t>UK declines to join US naval blockade on Iranian ports - Crypto Briefing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Patrick Bruel accused of sexual violence: the singer targeted by a new investigation for attempted rape - 7sur7.be</t>
+          <t>UK declines to join US naval blockade on Iranian ports - Crypto Briefing</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:38:00 GMT</t>
+          <t>Wed, 15 Apr 2026 10:54:43 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZVVPVVlPUjdjdndDeU5IbDEyMUZuZDUtUnJKUGRrRUhVYzZrcVBIaFNjM0ViZUp0U1hzMENRWDh5RzdhTUJibzRYS0Znbk1BaFhmU1ZpUm9Jcmo5UUhZdzRKMlkzeWxwT2dNWVpsMmYycTFQTS1kTlEyd18zcktuMnN1cW5WV3BvNTVDRXJLT3FhTVNESGViZk9hVEhOT1JvVFVVYnRjN0dtRUs5ajJCRzdZc2JRZkk2bUJabHdYdUdtTWFnQy1EeWliMEZEMy1oRlEyZmVaeDc4YkZpaUdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPREdEb2xvMG5lQy1iN1FHbVZHdmRHSV92VF9sX3FiYVE5dGJVMVpoTXZSbTlrTlhULTBtRWpkX0RmUk5Lc0RVallMSEFsdGlxQjR5X094Rmk3TDFjbVBOQUQ0TVctbHpueEFwT1lZUWtPZFFBZUM2S1BXZ3BUUFZQd2pVWHJ5ZzFSNUE?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2550,52 +2550,52 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46126.73472222222</v>
+        <v>46127.45466435186</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Politie LRH organiseert gratis droneopleiding voor amateurpiloten: "Goede intenties, maar kennen wetgeving niet" - VRT</t>
+          <t>Salvini: “Remigration Summit? Sabato a Milano una grande manifestazione pacifica del centrodestra, anche con trattori e motociclisti” - Il Giorno</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Police LRH organizes free drone training for amateur pilots: "Good intentions, but do not know legislation" - VRT</t>
+          <t>Salvini: "Remigration Summit? A large peaceful demonstration of the center-right on Saturday in Milan, including tractors and motorcyclists" - Il Giorno</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 06:13:42 GMT</t>
+          <t>Wed, 15 Apr 2026 13:29:43 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQeEo0WGExZjUydklnQzdRbmpFWFNpSjZSeFRjMTNJUnJRMWR4XzRmTXEwZ1B0M2VrNTlfTmpuOUhnSFVZQUJVRjBlMGFIalIza2IwSU1RZFVTMjl3Wk1PVGVkNzdvNXdzMnBOYzd6RHVseW5SeGpnb0JaSW84VEFLQjdxbk1fcWVteFpieVdiLTBmQkRvQ2dMeUlkaTg2NklCTFBaQURvNGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQOTVFUGhaZklEWXUycXRPMUtua0FJeEtncVR1dVpSRk00Uzcwa3VCRmNJOVpUM1owLVg0UXc5eGxLSzRXUGstRHVmU3lpMU5ZWHZJcTVfXzhPWWd6UzRnY1VaZGhmeU5nOU8xLUtkNDRUbXN2NXBHOXlsTDA2M1dHR3ptUHVLWF8tWm1iU2Rjbkk?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2605,52 +2605,52 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46127.25951388889</v>
+        <v>46127.56230324074</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyclisme : Tour du Limbourg - tv.moustique.be</t>
+          <t>Logistica. I lavoratori della GLS “fermano tutto”. Prosegue lo sciopero - Contropiano</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cycling: Tour of Limburg - tv.moustique.be</t>
+          <t>Logistics. GLS workers "stop everything". The strike continues - Counter plan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 22:02:34 GMT</t>
+          <t>Wed, 15 Apr 2026 09:06:45 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBZSlotMEs5bW5JUXE3bmN2NlNUbUQ1c1A4V1lydGZPMW1tZ3liVDhXRzhVMkJqZHdsWkYwWUtpOGZFeDBVc2EyenFtLXJuSzlEVDAtdTFZYnFnOS1PMTNlc25FOFRXMHFsSjI1cGg3T1NVV1lodElNb0RRcXZfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQNUE0WlQ2OERtcTZLbWJkaU51QlpsT0k4NXpDUWkyMndtS2lLTVREaTVwa1RjSkprT0VzcFFaTXQyYkJuQXZDNlJrSXdQZk1WVTFhZGdFQVJCT0VXSTFVWmU3ODJjMndRSEVHNE1fS2JfMlJXSWUtcm1acG52T1NkdWRzQ21GN3JsaTBjMTZkSEpPR3RVenN4M2JUaEhmQXpDZXgwY2w2T3dmLVZ5dnY2MWZGRVRjQ0dhQUxJQllxZzJ3NUdLaUhLdXNfU0IwZ1g2S2VN?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2660,52 +2660,52 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46126.91844907407</v>
+        <v>46127.3796875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tour du Limbourg - Les sprinteurs ont une nouvelle occasion à Tongres vendredi - La Libre.be</t>
+          <t>GiocaMi 2026, il Festival del Gioco da Tavolo - Virgilio</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tour of Limburg - Sprinters have a new opportunity in Tongeren on Friday - La Libre.be</t>
+          <t>GiocaMi 2026, the Board Game Festival - Virgilio</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 11:36:00 GMT</t>
+          <t>Wed, 15 Apr 2026 08:41:29 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNYnF2OWZyRjlEcms1dkMteHBFY3lZelZsV2Z6aUtweW1WNVcwdFpoOUFyemRiVTlZaHZIYV9wWG9wSk1iMV9QMlJhNGxxY1A0QmloTDZQc0psR0t6MjJTaFo1WjkxLUhIeWJLWnB2bVdMU3QzS2toMnNJZVdnZXdiRS1BZDFKQ01YUG5uSU8yWUE2WjMtSno5dEdvSFFkb3JoMjgxSWM0aEpHVlBKRGJaY1RQWnJnaWhzMHNMNDZFSDBlOTc5dGhBV1FHMTVqU2xaeDFqeFV5RHZmUVhfZ3BfN2ZxYVlsTDRpMEEyOEFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQZld3VU1iN2d4UWVBVVRTeF9VR2tQUUZQUENmLVFsUkFKSmFCbkY5TUNzbnFDVmJaeTY0WGV4OHJ0T1BZcVFUdDdvUzktSFBFUGQ3QW0yRTItTFVEX201N25VN0xyNkkxd3J4NnItZzRDSDliVzhYQTZaajVERVdCRGNWd1Jia25wVEhvcjNSQTZNcmg5TW8wYU9ES01FSTNnRzE2UkYyV1JwQnlKMmpxSktxR2ZPeXNTcjhIUGt0MG4yblZyQ2ZUUmxfLVVwNU83dWlhc25MWlkyWTFSbFZucF9wMzhYS2U3bVI3ME1VbG9VVzJxc2oxM25kMGdSdml4cWtqMmd5eG4?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2715,52 +2715,52 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46126.48333333333</v>
+        <v>46127.3621412037</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Loi Yadan : des collectifs d’étudiants annoncent « occuper » des campus - The Times of Israël</t>
+          <t>Lega Abruzzo, sabato a Milano per la manifestazione sulla sicurezza - ilpomeriggio.it</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Yadan law: student collectives announce “occupy” campuses - The Times of Israel</t>
+          <t>Lega Abruzzo, Saturday in Milan for the demonstration on safety - ilpomeriggio.it</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 19:00:00 GMT</t>
+          <t>Wed, 15 Apr 2026 12:28:22 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPSXg2c1k1OU9PRU54OGpYM0VrdTJheEJ2LUZCd1VObVpjYXdNZWVFSTNON0ZQWTQ4R05HelNsMndGYWxEeXlGS0dfV2NidVNNaVBZZ1ZRYW5ONzlmdXB4QXVZNENZbU1qQjhXWS1ESDJrT2RoZEVFaGZ6ODBxcC1jN0RrdXBTTWxoX0JjdlpkQXRkYnQtcVlEZENB0gGfAUFVX3lxTE1ZYW5PNDBMb1ZzQVRXSk9Nc1FsRC13eWwzQW5HQXFWa0w4TW5TTTNKNVlFckFzMmNOeEFiMzZFVHd2LUszdU16VHprWWd6YlVxZjhrZEdmRVUwSnA1WFZfYll2UWU0dF9yaHE3THY3YUNBTHMwQ0xHMTlVREtZUHg3SnNEdUhkRlBGZU1nOWpGczlVdHg5S2g5VkVBdnZnYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNdkZ0blR2TjFPa08tcUtZb0NpRWpyTU1UdGZaRkxYdERZdlVENTRtcWQxR3BPa0F4V3RMZDJJQmlCbExjUEk4eFUwcFo2Mm9ZUWJYQ3lZbFdrbFk3bXQtZXE0RzY5WGpNekZiWFlDTklqNVZsMnBNaGxRR2ZOVnhmN21FYURidTRGUHp6OEtpWHhlWkJfOFJwcHhLNlRPZHAxWHBwSmZ3?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2770,52 +2770,52 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46126.79166666666</v>
+        <v>46127.51969907407</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint-Denis : l'arrêté anti-expulsion pris par le maire LFI Bally Bagayoko suspendu par la justice administrative - CNews</t>
+          <t>Al via la seconda edizione della "Don Gnocchi Run" Milano - Fondazione Don Carlo Gnocchi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Saint-Denis: the anti-eviction order issued by LFI mayor Bally Bagayoko suspended by administrative justice - CNews</t>
+          <t>The second edition of the "Don Gnocchi Run" Milan - Don Carlo Gnocchi Foundation begins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 18:37:00 GMT</t>
+          <t>Wed, 15 Apr 2026 09:49:28 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNQm1EOXpOZWpSS05qTmtyS1VObWhuZ1ZCZFBfOENKOTkwTm55alh6TTVxSjBnTko3VzJVWlotZWhUQW1ES3FTV2VBdGtkSGdwc0lHMElpbTcydEx4anl6QXVRUXhOU2VFVGVIZGhZdHZIemw2RDRjbVNtTFRxRlNVanlnSXdFZmFaMi1IRE54Q1RVX2lOYWFyVzRIa1lSRnFibHlrY24xaHZ0aHJQN0pXWXJuMDhGZzlxUXZfWFg2ejTSAcABQVVfeXFMTUJtRDl6TmVqUktOak5rcktVTm1obmdWQmRQXzhDSjk5ME5ueWpYek01cUowZ05KN1cyVVpaLWVoVEFtREtxU1dlQXRrZEhncHNJRzBJaW03MnRMeGp5ekF1UVF4TlNlRVRlSGRoWXR2SHpsNkQ0Y21TbUxUcUZTVWp5Z0l3RWZhWjItSEROeENUVV9pTmFhclc0SGtZUkZxYmx5a2NuMWh2dGhyUDdKV1lybjA4Rmc5cVF2X1hYNno0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNYkhSU0FSeXlUNkFoLVlEYko1YnJGNTdTNTYxZ2dnbjhodEJyNzJ0MXhDOXBXVGFQdlNrRF9Obl9DcmluN1RTSWdzdVdEZzFTeG9sZmw0eGVST0pXYVZWd1RIVUg0YVE4WDNtOUxRd2pkSTA3bkpDWVhJbmFibFo3cjYyS2hwVmZpS2NIVnlQSDJYTXQ1WFZNN19TV2dqNGgza1dyWA?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2825,52 +2825,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46126.77569444444</v>
+        <v>46127.40935185185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Misuse of laughing gas has become widespread in France among teenagers and young adults - IslanderNews.com</t>
+          <t>Salvini e la piazza di Milano “del centrodestra”, ma non ci saranno né Forza Italia né FdI - La Stampa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Misuse of laughing gas has become widespread in France among teenagers and young adults - IslanderNews.com</t>
+          <t>Salvini and the "centre-right" Milan square, but there will be neither Forza Italia nor FdI - La Stampa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:03:30 GMT</t>
+          <t>Wed, 15 Apr 2026 11:33:00 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNeG5lVlpCUHY3bnJzUGp0MU50TWlvd01fbTRfeGc4MEw4ZXEtTktxQjBIcm1tbElQdC13T2I4S29QbnhtQWQ2T2hpdTF3dHNGQkx3NVhrZEdtOThtRGtiZWthNGtBd05nUUdnLUQxd2pxVHV5VzR0MlZkNlZsYmc5cW1GTjJLS1pPSmtWZnNGWVNOWEJsR0h0RmlJLTFzU2FsRWlUTVdyT3RkWXVJMHJ6NEtUdnlobllzUkJTVzEzejRTVy1DWDl0N2FMcDRTZEdJcF9FZk9rUHFoQlhCUEp5dVdMX1RPSVp1bzFTYUNXaVVnNFZ6ZDNlQlh6RVFfR0FpQmZYQW0ydEtOZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNdWphekViMVd6LUpKdWVmS05tY2tQMUhzczRwZ01Uel8yU0steVJxeU53RFFwdlBQRnVWel92UUcxdHY0VnZLWWtPOElzWml6SkdtVmlRWW9Ga0dRR1RMbXFOSHhFMXNLTU1BV094NXJyZm1HVUg0ckVOSXc2bGlZSjZZTF9uR0dYRjRaV2JQWGFiMExhbEJFdm9GZzlrXzV2dzFzSElWcDByT3pfU2psZzZaT0xaNVNvbFlBNU5kbzlXcl92ZW5hVDI1VmhBaUpkcFFLczNmNE8xTW5XUXU00gHkAUFVX3lxTE91UXhidUtvRWVPRmN5T0JSSUtKU0ZTb0x1WjRWMWNyUktnN3NTNkI1aEJ2UzNRVzNrM3RTNHJkVW0ycElxeFIyc3BZelVqZW0ydDE3OXBXY0ZJQmxrV2tlVFZNN3dzcGR2SUdoWjVfOERMRnNXTHctWk9UZm9VMmlTYV9ad01xbkZTMVpSRl9XWkVLOEQzZXhyOW5kR0o4UEY2b0dsWThBR21ZZkh4b1pDYnJxeTdObkdmNWQwUHNDbWlSMXFPOXNtY1NSUzVid3lvcXpZcDV2aDlDNGk0Wk56Z0g1dA?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,52 +2880,52 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46126.58576388889</v>
+        <v>46127.48125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City Germany English</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich" OR "Stuttgart" OR "Germany") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror attack" OR protest OR strike OR riot OR "hate crime" OR "antisemitic" OR "vandalism" OR "attack") AND -football AND -soccer AND -Bundesliga AND -Bayern</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lufthansa pilots to strike again for 2 more days - DW.com</t>
+          <t>Tutti i numeri della Milano Marathon 2026 - Runner's World</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lufthansa pilots to strike again for 2 more days - DW.com</t>
+          <t>All the numbers of the Milan Marathon 2026 - Runner's World</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 23:43:38 GMT</t>
+          <t>Wed, 15 Apr 2026 08:46:45 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVVJnQmMwYzljUGFtaGpVU3czbEpyNThYUkx5ajB5Tjc3eTJGaUFHTnBqZmFzN0ZRMUtfYUE4dDlTd3FLUXVTdVdOQS1mbHVtbmhjVmdXNFpNV1BDekZieTQ5NnVmLTVMUlpRYjF6MkhVeEVRRDAxT0thc0xBcXEwLV9XamxkUmNiRVBGdnB4Tmt2bURjcVRRZ0FiTnpqVjRmR2ppLUFoalREcURmMU9jSGlaZWo3OHU5ZkJ2V1Z0M2t5a09W0gHEAUFVX3lxTFA1YmNiVExEYzVXdVVadi1vN0R2UWF4NTdGWWFOQmFaWE5CYkJhR3BKNmVEVmRld0VicmtaY0tSb0ZsOFBabEtNbFQ0ZWRUM3VyYTJCamNrdGNYc0dzNlFocjhlbU1tODI1OUxIM0RxOVFieXI1WngyNUhjakRjVnF6b20wRElOa1FqOUlNbEM1bi1EQlF4Y1N1SVNWd3BtV0ZZd0d1UFNvc01mUWRoSjJLSFo2NHdNNkMzNU9sb2dfSTNyUzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOM1V1VUMycjZaQTRTVWFPRTNEaFpmbW1yOHl6djNiSkJJZFZaV0Ytb1JzSnQtMlJCNjlta3RpX0M5ek8wUVJNcVktckswTFBJOEVjOWhiTDh2ai15TUdSYUxFbVhTemRCYkVLMi04anRpWXNQSWJpR01TWVRqUTIwdQ?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2935,52 +2935,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>DE:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46126.98863425926</v>
+        <v>46127.36579861111</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wertheim Selected by California Redwoods in 2026 PLL College Draft - Brown University Athletics</t>
+          <t>Orienteering: a Bologna i parchi del Navile domenica 19 saranno invasi da mappe e bussole - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wertheim Selected by California Redwoods in 2026 PLL College Draft - Brown University Athletics</t>
+          <t>Orienteering: in Bologna the Navile parks will be invaded by maps and compasses on Sunday 19th - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 01:05:49 GMT</t>
+          <t>Wed, 15 Apr 2026 12:12:42 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNdGlqaVJrN19wNU1FbVVnaF80WTRMSGE1WnNXdV8zY1lTSlY4SkxpZmhNX0g5S3FfZE5NbXk4WWZsZEdxeldOcVRFRkczR3d2ZXBEczdjSExYSmJ2R243UHR2OUE0b3huaHBicVNxOGowQWQ3VDdwa2FDc2MyWXB3ZzNQcVV6YVRiZFVCX3FUTmtkRFVfaWVMWjlRbmlNM242cnVTUm1tVk8xaWpscER0dFNwbVZjaXZLVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOSTJsd3dReERaNXlPMjZlaEl2ZDJNaHAyWXVzZlZGNzJGNC1LSVExVDhheS1QOVJwQ1pYMU40dUNXb3Z6RFdSVjlaR0xSQUFKLXhnNW5RRGl1V05hS3ZDcU1mZGhMOENOSzJSMWpUU1Z0dE9kRzlqeHpSVWt4NnBPaHVOcEtWS3RhaklHRHQ2VQ?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,52 +2990,52 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46127.04570601852</v>
+        <v>46127.50881944445</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A new exhibition asks whether design, like corals, can give back to the planet - The Hindu</t>
+          <t>IMBRATTATA CASERMA GUARDIA DI FINANZA, GUGLIELMI (SAP BOLOGNA): SOLIDARIETÀ AL SINDACO, GUARDIA DI FINANZA E REPARTO MOBILE - sap-nazionale.org</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A new exhibition asks whether design, like corals, can give back to the planet - The Hindu</t>
+          <t>FINANCIAL GUARD BARRACKS DAMAGED, GUGLIELMI (SAP BOLOGNA): SOLIDARITY WITH THE MAYOR, FINANCIAL GUARD AND MOBILE DEPARTMENT - sap-nazionale.org</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wed, 15 Apr 2026 00:09:23 GMT</t>
+          <t>Wed, 15 Apr 2026 08:45:02 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOQnpwb2laVFhrN2JGVk1LeTNBV0RoUUFtYWNSd2lFdFR2TzVGZnJLRjB5LXUtRlpvYW1KWndjVFRtMDJuXzlYMElIRWJGTkJiNkRKR05FQ0xjTHJJMGhPTFJtUXctUzhId3JqU2ZrX3BTcU1pN2YyR3hQc19UMEswanJsdWJuS21ZSkhaYUtvZVZnVmFMeHhuZ3FfTTBuXzRINnpYNU44VDNNYlJUSlk3eERVY25RSVBzUlNMSlFHT09mSGJSMlA5bENHYmQ4NW42bk0zTkZweThqN3lZeHZGY3dn0gHiAUFVX3lxTE5CenBvaVpUWGs3YkZWTUt5M0FXRGhRQW1hY1J3aUV0VHZPNUZmcktGMHktdS1GWm9hbUpad2NUVG0wMm5fOVgwSUhFYkZOQmI2REpHTkVDTGNMckkwaE9MUm1Rdy1TOEh3cmpTZmtfcFNxTWk3ZjJHeFBzX1QwSzBqcmx1Ym5LbVlKSFphS29lVmdWYUx4eG5ncV9NMG5fNEg2elg1TjhUM01iUlRKWTd4RFVjblFJUHNSU0xKUUdPT2ZIYlIyUDlsQ0diZDg1bjZuTTNORnB5OGo3eVl4dkZjd2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQMVlISURqajBGSmVlXzhJY0ZBWmw1QUhHaXpENHdXUlJWSFppeUlPTEh4dWw3eTNXYjd2cVBpT1J6TUxteGpsekhLSW9XOFVrRTNzNU9NcVpILV9MVXdjcEMwOUFhUFAxa01LUi1SY19OVlB5OGhNdk1JZXFkblUxM2tmOE1DZFg4b1dtRl9oZWVnQVJzY1J5SzRzVkNoY25WVnp6c1c2d1ExTUVvTV9naDBLbjMtUGZSbHQ1bTV3UGZGRXlxbjBNbnhzZ1o5MXYxUkdqR1pZYmpvdjh2UUtwNWFlZE85a3JJNzZjUjQtLWdkYldvTlQzLQ?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3045,52 +3045,52 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46127.00651620371</v>
+        <v>46127.36460648148</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>Hate Crime Europe English</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Audi expects no more dieselgate emissions provisions in 2018: CFO - AOL.com</t>
+          <t>Reform urged to ditch London council candidate who shared vile Islamophobic posts - London Evening Standard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Audi expects no more dieselgate emissions provisions in 2018: CFO - AOL.com</t>
+          <t>Reform urged to ditch London council candidate who shared vile Islamophobic posts - London Evening Standard</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 22:48:28 GMT</t>
+          <t>Wed, 15 Apr 2026 09:58:40 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOTWhvM24tdU5odFdKVVB3RE9tT1g1SkljNlNhbHhSYmRydGw4am4tRUc4VWNzZUlxeXpuV1BuTWs1ZTl3ZmROWjUzOFVOMFVoUHRZSGdhOFMwRGxwZXZxbG9DTllOeUdBQ216bGNaRFNWbDZRMzNuNjNhb1VOT0NQcVQzLWc3TGNUSVRoWklZU2xlcW5VRzZYeUxCTUhTWTNRSE5N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTNzdk5Yb3p0VTZ0MGtUdHMtRkZYTm1fMXFFS0N2bUtnYjVkbXN1dzEzRDZzemRJM2k0eXc2ZTZMb3lXa3VaTlRpeFZ3enh3R0xWVlF6MTJsdElIZ0ZkaDJyaVlMb2tKQm9MR1B3dlViem1TT1ZRNUlVbE5vS1RCX0ZsTmdFMHkyd09EYl9QQlhCRGpZR1FuYWRR?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3114,1712 +3114,7 @@
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46126.95032407407</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Village Ingolstadt (fallback)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 12:33:16 GMT</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSWtjRGNLRks5MlRmM2JVc0hDLVZ0cVlKbUJUNWlaVm9WN29HMHl6bGlOblhEc1lsZ3lvWnhlb2RleGpXMTJRU2lwRVdIR0swQlR1c0lEbXR1cUtnYVVLU0N4bGJCVzRIcHA5dTBmQzhXZldia1l5M0FEZkIyWFJHMVlqVVk3a2Q5c3pkekR3?oc=5</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>46126.52310185185</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>High Level City Spain Spanish</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>("Madrid" OR "Barcelona") AND ("amenaza de bomba" OR "paquete sospechoso" OR "paquete explosivo" OR "ataque con cuchillo" OR "tiroteo" OR "atentado" OR "operación policial" OR "evacuación" OR "artefacto explosivo") AND -fútbol AND -fichaje AND -Liga AND -transferencia</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nuevo tiroteo a plena luz del día en Barcelona: la víctima, en estado crítico, estaba en la terraza de un bar y los Mossos lo investigan como un posible ajuste de cuentas - El Mundo</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>New shooting in broad daylight in Barcelona: the victim, in critical condition, was on the terrace of a bar and the Mossos are investigating it as a possible settling of scores - El Mundo</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 20:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1GUzI3dkwyYkc2TFRvQWVuenhEd1p5Y2ZDZG1KYlo2d0xiTUFQeUlWdV9fcjhoVm5veUVnY0JWYjI3RGlYZHZlMDJvRXZQSVRkX1ZLVUU1RHdoZ215YWJRa3JWbnRsRWZuaWEydk1VaEE1SFFrVTFibUtKYkzSAXxBVV95cUxONkhwNFE3Y0dOc0ZscmM2TUNvaE1HVVZUY2liNXBtT0RDZml3RndnRks2ZWZCdEpWcVVleE4xT2N5eGRiWnU3RnlaTXRhUHc3Qkc3SUhnRkZyMVE2VDBXZGhYdnJqSkF2VmRUVHNzSkRaUTRuMFVHeDZibWtM?oc=5</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ES:es</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>46126.83333333334</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>High Level City Spain Spanish</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>("Madrid" OR "Barcelona") AND ("amenaza de bomba" OR "paquete sospechoso" OR "paquete explosivo" OR "ataque con cuchillo" OR "tiroteo" OR "atentado" OR "operación policial" OR "evacuación" OR "artefacto explosivo") AND -fútbol AND -fichaje AND -Liga AND -transferencia</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ajuste de cuentas en Diagonal Mar: un herido crítico tras recibir varios disparos a quemarropa - El Periódico</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Reckoning in Diagonal Mar: a critically injured after being shot several times at point-blank range - El Periódico</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 15:09:08 GMT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNdFdLSjYxQWNmZjJqd3V4b2xzMmp5RWhXNzR6dXBMYjRwMkd6SWNsc3FlX3VEcmRPN2xTdnI1cFdwbWx0eV9pTE1LRUtydzZUUXRtRjBkYzBZNk5GVW50UHN5MzYxQUVSS3dzWG5Dd21Mb1l2dExKbkdXNUszN0NSY1JmTmEtWjduYkYtc09zNnRVa2g3UzVUYm52eU16UTNDTlRzYk9tbzBLZ0F2bER6OVNoam9NWW95M2o5MzhQZVVSbGFGNEHSAcYBQVVfeXFMUFVpWlpxT2Z2eVI2TXhLdks4TmNGa3RGbUtaY3FCUFd1dy1UaFZjaUhfVExfOWJ0bVRyQnFDMzNDN0hjNFlUV214ZXUxeHdWVTJsYmhOYU5aZm1PdGRrbHVNWGJOMWFvY1dqdkpoN1lnOGNuUV96VDJndW90VHl3b1ZjSE1seTFSWnRfaWlhTWN4N25HZC1pNDRrVnZwMUNudVp4dkxwTnpfWERlemxSMjBWM1dCWTYxeW1WYXpPZGt4clJjbjV3?oc=5</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>ES:es</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>46126.63134259259</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Village Las Rozas La Roca (fallback)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>("Las Rozas Village" OR "La Roca Village" OR "Las Rozas" OR "La Roca") AND (shopping OR outlet OR luxury OR retail OR news)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Las Rozas becomes the battleground for burgers: this is how Spain’s best is decided - Madrid Secreto</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Las Rozas becomes the battleground for burgers: this is how Spain’s best is decided - Madrid Secreto</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 10:32:26 GMT</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNTlVSTXh0dWFyWEZzam5EWWFOSVg1ZDRRYlpCNm8tb01nMHVzRTFsNUhwbmg4bE1RMlhKN01nTnRONU9CdEtrMzhubWxHV3JwdGgySThYRVBfY19SeXJIOXp4aDRTQVF2Q0Y0bnY5TktHZ1ZUVU50Z3NaU3djeDlpdkxHeF9Kc2c?oc=5</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>46126.43918981482</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Second man charged over Finbar Sullivan stabbing in Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Second man charged over Finbar Sullivan stabbing in Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 10:28:15 GMT</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5mZVRyTGZXV2FMTWpNYjhKNUV4cUdYbjhJSFgyREV1WDVNaDVLRENLdm03aU5xdkJqSkxzZ3VjYTNEaWpqRVJiaEhndWZONHNTMW1qWDdLLVJEUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>46126.43628472222</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Eghosa Ogbebor shot dead in stairwell by boy, 16, Old Bailey told - BBC</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Eghosa Ogbebor shot dead in stairwell by boy, 16, Old Bailey told - BBC</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 12:02:53 GMT</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE91RW4tbEo2djNUTUljTVlFb2NMNEhUb0dadk40RE0zZEdacHhYVHJHVkJRLTV4cnRlUFQ2bmcxZngxakQ1U1B5N1ZRR0lJeUgzTUtSMTBPUHUwUU9Q?oc=5</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>46126.50200231482</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Fuel protest causing disruption on N13 in Donegal - RTE.ie</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Fuel protest causing disruption on N13 in Donegal - RTE.ie</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Wed, 15 Apr 2026 06:55:06 GMT</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFA0R1RSaTFRZ2RTUUJtTTZVUXVlbTQzbHVTRl9KWnJEdEVDblV5WTJfVmJWMFUtT0dGakVqME4wVmM4MUVWRVFtTThzLVNtNUxueXY2S2JycTE1ZndTcU9pWE9kcXdzZjJoN0lYa0NKYkZUWGFxQmJKb3VUZw?oc=5</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>46127.28826388889</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Farmers threaten protests in two weeks without government action - The Grocer</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Farmers threaten protests in two weeks without government action - The Grocer</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:50:11 GMT</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPMVlQZmZnaEFrRmpFcmNZMXRVVGJ0SmNIVVFueHdvSUVuTEVvTW5odTlyZElUdDJOeW5fSy1OQ1FSY1FHSUREV3FJbjZ0M3dVLXh2WXQ0WEItRFItaEx1QXZhQ2Frd2FaYUNsWXprTmZ3bFhSdDdadXU0bEt4cFRrZGMxN0tjRVZHakxseFMtOGsydkJHazl6c01vTEFBaE5uUEw1Y0xvbHRzTWl1U0RpNVZ3?oc=5</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="n">
-        <v>46126.78484953703</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Fuel protests lead to key vote in Irish parliament - BBC</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Fuel protests lead to key vote in Irish parliament - BBC</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 16:53:44 GMT</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBNM3JZdVBlcVVQdlNLdDd2aTFURVJXNmNMVDJqRms1Y3dydjRLZ2lrVGlDSzlvYjcwdDNkRE9VTDdsNlZiN0FqV0ZjNFllc21GM19rWmRwYWJ0dw?oc=5</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>46126.70398148148</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Moment killer laughs on night bus after stabbing student to death in south London - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Moment killer laughs on night bus after stabbing student to death in south London - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 19:33:59 GMT</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNVd2Uzd1cmVRWVNYNnF2R0JYaFFaTHRXMHdfSU1WcjhvSDYyVjVnUmdaUXliUWdIbWlCYmdyVnAxTkZjTWxHcWFwTDIwcnBHX2lQTENvbHRhOTl5cHdmdXVYdmQ1aW41QkZPZno2NHdBaXV4QjBHMUg0T1l5VFhVbTdRZ1FNY3hnZGo1TDVGYjNmOG1EMS1YX2E5R3ZGRTJZUXlUOTMxUnN4Z19neWpvWlZTZVZfY3B0MGU1Mk5Dell5d3c?oc=5</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>46126.8152662037</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Irish government majority cut as two lawmakers quit over fuel protests - Reuters</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Irish government majority cut as two lawmakers quit over fuel protests - Reuters</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:44:48 GMT</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOOWtXMHV2Ylo4WE5jVTV2bngwUmllNk9nWHlYNGF4d1F5cnRONkNNYVZ6N3lNOVJvaS1JRVhYSUtYSXNObjQtdFlEMzdaWHk2WF9ZVlB2aGREQmZlM3MzMUljRGZpald4ckNTTGdpNFFqaURaQ3BhQ3Q3ODNUOS1ESXhpV0dfMVlFa1hSRmJmVS1MaTlYblFZS05YUENydUdWMzF6TWtQMHQ1QTdSeXNFaWJwYw?oc=5</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>46126.78111111111</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>A city united to resist Britain First – hundreds to protest against far right - thecanary.co</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>A city united to resist Britain First – hundreds to protest against far right - thecanary.co</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:20:36 GMT</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOclJzb3FlbElSWlFCckNEVDQxZG9uTVlEOEFEdWI5VGlSUWJrMm9pMngyMnlSdlYzclpOUWtFWG03Z3BOUEFwdjNMSFFkelVnU1IxZDByUUxNZjMwLTQwSUlMTTNOemVQcW9LTnRQQ3oyWmdMNUxZMFdvZjJtWDZxYzRMUERIVzhnUFBGNXl6U1JYZ3BOa3FucFhIWUZiRWU2b29VRVRhdWs2cVBjNVBhaXdHQ28wT0xiVHBkWA?oc=5</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="n">
-        <v>46126.72263888889</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 10:58:00 GMT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQZTZ1aU9ULWZDREhGLWtWQUVXNk9mVVN2ek84MkhkUWJDbUhRMzBlZHUxc3lvYThnS1E0X1BUMkhHY0h4Qk5GZnJaeGpKclRJdmJoSGdocEVaQTQ3aFRIdEFMbEdMalVsc0VNaXZUb1VXWEZSc2xqNGxTQ2NfdEpWQXdvWTEzV04zTlgzeWVKYWxGWjNMU2ZGRnhtbUtLdnNwUXYycS1oVlJQV195VTZtRHloX3EwdS11WEdXMEZ5Y1dMNE41VElUc3VwMUhZWFZmb0hXQVRIeFM1aERvbFByWUpZeHVpRzVFdmRwT2ZMUXh0anpFSjBCbXk1aDl2TTAxV2x0a3NSVGEyZlZp?oc=5</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="n">
-        <v>46126.45694444444</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Fines issued after fuel protests across NI disrupt traffic - BBC</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Fines issued after fuel protests across NI disrupt traffic - BBC</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 10:58:53 GMT</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBYR2R3X3RReFM0UGt2MERBdmMyV2lMNzJaNF9SVDJibVVkTm1TUDJSVVdhZWppTUo1TkFYWVNBOGZnWG82eEhxX3c5bUpNRGlmSTF6WFEyclBFUUJz?oc=5</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="n">
-        <v>46126.45755787037</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Five bizarre things that happened at Reform UK's rally in Scotland - The National Scot</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Five bizarre things that happened at Reform UK's rally in Scotland - The National Scot</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 09:03:58 GMT</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQR01hZGdHSWJTaXpEUGVMcTBDSU1ReVJ6RmlNZERWY21GVTA4Z2NjUFdkc1p4ckhSRGN4Rk1JNUNwNHdfdlYxNjNKT3Y5RGZqV2Z3bmg4VnI1bmhabnZGUENXcHlnYlR3WHBLM3A1STRoZUd3MUw0akJnbWhTdnRGNnI2cm9pQUR2Tkw2Mi1rckFjNzh3V2xRUHpOQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="n">
-        <v>46126.37775462963</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Why and how is US blockading Iranian ports in Strait of Hormuz? - BBC</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Why and how is US blockading Iranian ports in Strait of Hormuz? - BBC</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:10:52 GMT</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBicFVNdC1ySlBTbkpVQVJCaFU4a3VSeUh4MElpWGhleUJIVnZKMjZBNE1mSXI4ZTNPQWM3bEx2UkdxajJYZ1duM1RMUHRyYnVmZlVHcjBaSExrQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="n">
-        <v>46126.71587962963</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Nuovo sciopero dei dipendenti della Bologna University Press - Virgilio</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>New strike by employees of Bologna University Press - Virgilio</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 19:15:59 GMT</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTGhHRDBlUDNmS2NZNmszamFLMHM0OWliZ21kQXJxdjBsM2NvRF8xRloxcjZXcmFwQUxCNU9JTkV1dmdheWpWdDVwbm5LUUVPMXNGSmw1RWFHMVVLWHpRZi1kSlVwRHdWbmk3UXpQOWpINDV4QzMtaVlCRTlIQ3YybTB5QmtjZThlbFJ2aWJaYmpHUl9PZ01WcjIwa0VVSHFZdG0xUEFYVFAxX21zS19oSFRQbmpsQ3N6TC1oc2VEaVUzYjlJZDhDWklya9IBywFBVV95cUxPTGhHRDBlUDNmS2NZNmszamFLMHM0OWliZ21kQXJxdjBsM2NvRF8xRloxcjZXcmFwQUxCNU9JTkV1dmdheWpWdDVwbm5LUUVPMXNGSmw1RWFHMVVLWHpRZi1kSlVwRHdWbmk3UXpQOWpINDV4QzMtaVlCRTlIQ3YybTB5QmtjZThlbFJ2aWJaYmpHUl9PZ01WcjIwa0VVSHFZdG0xUEFYVFAxX21zS19oSFRQbmpsQ3N6TC1oc2VEaVUzYjlJZDhDWklyaw?oc=5</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="n">
-        <v>46126.80276620371</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>La Statale alle celebrazioni per la Festa della Liberazione - La Statale News</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>La Statale at the Liberation Day celebrations - La Statale News</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 09:53:14 GMT</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE45UDRvMTRfcVI5bm1fbHVGWG1BUmE2ckNZclFhVThnOWVqQzZ5VkFOQVFzdXFDamlNVzNBUDN6X0txcHFHN1FnWUxiU0VEMEVfemFvUDBnZ0dpSVB2ZFNCcl9PSEMtVElpMjk4ODNBNFJkNElFUU9vWklRWVppZw?oc=5</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="n">
-        <v>46126.41196759259</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Scuole Aperte metropolitane: pubblicato l'avviso per la coprogettazione. Il 20 aprile la presentazione online - Città metropolitana di Bologna</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Metropolitan Open Schools: the notice for co-planning has been published. Online presentation on 20 April - Metropolitan City of Bologna</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 10:58:10 GMT</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMktzclhSVDltOF9YNnVUQnhiTDBsQTF5Q0F5WjNJY25seHlySFpBelZnUVYyU09ITlBBay1aMnJOUnlmaEFJLUpZOTdiTVNmLWpjcWphcXdMVmRBVzNyNVNla2pEbkJaNm5xOEJ3Mk9BbUlnbXFTcjRjRmlMRmtvYVBicnhSWVNtNjVCd1dkWEFPXzlraGpzOXpwblpfd3B0NzYtZ25yR1RzRmdHVjNqM2lxVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="n">
-        <v>46126.45706018519</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>La Lega in piazza Duomo. Cassani: «Basta casi come l’egiziano di Cassano» - malpensa24</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>The League in Piazza Duomo. Cassani: «Enough of cases like Cassano's Egyptian case» - malpensa24</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 15:30:05 GMT</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5KWDhwQlhWWF9aQjNRNUhLSnV3Q21hZktJZnJsaVAxc0pMNXd5X2dGcTVjWFUwTGl0bFZqbGpjSVdvRXRNLXhQNWRpOGlVNTdVSmd1cGZpdWxWRVEyWjdreFJqdXFCNG85TVVVYXNn?oc=5</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="n">
-        <v>46126.64589120371</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Blitz dei tassisti agli stalli per Uber in stazione Centrale a Milano: interviene la polizia - Il Giorno</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Blitz by taxi drivers at the Uber stalls in the Central station in Milan: the police intervenes - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 09:05:13 GMT</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZloxcnBFQlNnUXRLemZfR1h6X2VuT0pEbGlyWjN6TkJXSlgweVIzNmFUS1F2VjV0ekg2VDg5QmFqSncwd1JHeG4wODYtVTFFY3R4WXljM0pJR2YtblZHSzZkUV92dmZkR2hFMzluM1JOZUpuakJsR21Cc1hlWV9uN2d2dkQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="n">
-        <v>46126.37862268519</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Giochi olimpici diffusi, Torino Milano e Genova candidano il Nordovest per ospitare la manifestazione a cinque cerchi - Linea Italia Piemonte</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Widespread Olympic Games, Turin, Milan and Genoa nominate the North West to host the five-circle event - Linea Italia Piemonte</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 12:44:00 GMT</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxPeHlMbDhwOFRNQzh1X2dsSDRfa1VyR3czcjIzSnMwU3Z6eUR5YkRIODZUdkszMTRkemVObEJBY1BscmdHQ2UtZEU1X0gtNjNxNUpGNi1zR0Q2bU9hd2p2MDFEZmJtSjNBekhNODNUSlR1R1hTSnJZOTJ5VlFoeENzbTMxZl8wR2N1RlBWdm41NXRSLXdWdVlJdktpbEFMUUg2dXRxSXFDUWlMaUlXbEFZeU91QkFuc1NaU0U1X3k2THZGQjRBVTIxSzQ2cm5RdnRKUXVrUHJFY0FWcml0RHdXUVUwOE9QUjhULVJpa21SSjdUeUhvcnRTOXllR3NOdUtkci1Wem9WaHQzcHFLVnNPV0RHUXNQNWpJd0pXazRobHBNWUswcDhKcjlIWHY0dw?oc=5</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="n">
-        <v>46126.53055555555</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MILANO: “SARANNO QUATTRO LE PIAZZE CONVOCATE SABATO 18 APRILE” CONTRO LA CALATA XENOFOBA DEI PATRIOTI EUROPEI - Radio Onda d`Urto</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MILAN: “FOUR SQUARES WILL BE CALLED ON SATURDAY 18 APRIL” AGAINST THE XENOPHOBIC INCREASE OF THE EUROPEAN PATRIOTS - Radio Onda d`Urto</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:02:00 GMT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQNUpHQzM3TG9vZC1HT3E5UHdtaXpFUjVuQXU4R0hEUVhhTmEwUXhBWDlCVzRjQkhWU1U1U2c3RWRqc3FDejBYRnJyN2ZZbXZtLUk5cS10cWhTbFNFMXhPWklhZEhoZUJPaWg5WEVQek92cm1VRUhKclVXYTNnMkRELUFjNjJBSE5rYnYzalE0UWpTWXVQYzN2SUNZWFl5eUNISmZ1YzFhQ1FodTBDVDFBVHlfallYYnY3bjJrUmx2S1ZsdjVLTjZOenVkTFVuQnZxTGdwaWoyUWRWMy1iVWdGQnZR?oc=5</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="n">
-        <v>46126.70972222222</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Menarini bus, la protesta dei lavoratori - La Redazione</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Menarini bus, workers' protest - The Editorial Staff</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 15:47:52 GMT</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5DRG5BcFhJMnVYZTVDVThiaEh1Vkp1VVdyTk51b1lkVHNyNm1ueGRQLUlXUUxUekJrZ2RDUkJYdVl6YV8tdEd1VHdXMHdXcnJLbWdtZXlYSEx5Szl5bzEwUnByZjg3ZEN5U2F2NUFRLWpWckhOVWpj?oc=5</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="n">
-        <v>46126.65824074074</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Blocco di Hormuz, chi guadagna dallo stop totale delle navi - MSN</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Blockade of Hormuz, who benefits from the total stoppage of ships - MSN</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 08:12:22 GMT</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQVVpzNl9keWJkMzFlNzJPMkZobzZ5azRKWlJJN3p4VGRpd1A5MVNUMUlNbGRHTk1EQnZqTFA2Z282d293Q2w5NFlRTDdlME9vckJ1amVFTGYya1JoeG5sQ1NrcUpiMUt3N0JodzBxMmtkakpicHcydndoaEFpSUlhOV95b19pTGdYUlN4ZzdkV29KbWhScXFQcTZFT0xDeUdnNEVraDVWWkpweGstYUVBOFp5YUFLT0hiU05oN25hUU1oRTdyV0dRZTU0TEt3WVVoeUFwMXVPajZ0bFNVUnc?oc=5</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="n">
-        <v>46126.3419212963</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Chiusura anticipata di alcune attività e presidio fisso serale. Via alla raccolta di firme - Il Giorno</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Early closing of some activities and permanent evening staff. Start collecting signatures - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Wed, 15 Apr 2026 04:44:31 GMT</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNVDBKYTF2dnZVejl2VWE4UEdiSWhMVC1kRS1uci1LZlkzVlR2cjV0bTMtdENzZk9KT3lERWFyTHA0VFViaU1CbHFGUXlENnZLYjZFcW1oYmZvTllMYmZReC1iYTVIeGFuMTNmcWRlNGZEdVZQMmpxalFBWkZQbjVVTkM1WU5pS1pDbW1SZWdEYw?oc=5</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="n">
-        <v>46127.19758101852</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Minacce di morte a Lepore. Piantedosi: "Vergognose" - Il Resto del Carlino</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Death threats to Lepore. Piantedosi: "Shameful" - Il Resto del Carlino</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Wed, 15 Apr 2026 04:34:11 GMT</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOZl9NalM1MkNRTXMtc1Vkcm5ueVRPLUVIZ0lpX3g2UFRBWHNMeWQ0UnF0R2h2NVVrLWdPTFlJZl8xemk5dGJVaFV0WXdvdWNVSmtsNGJZMEVrRGUwS25yZWhJMGlzanF3MTBvbE9qbmdQZFZYemRXd2xfRDRSLWFycHlSUTZvZ0JmZnBv?oc=5</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="n">
-        <v>46127.1904050926</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Fontana e il Remigration Summit del 18 aprile: “Sarò in piazza da libero cittadino non da presidente della Regione” - Il Giorno</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Fontana and the Remigration Summit on April 18: "I will be in the streets as a free citizen, not as president of the Region" - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Wed, 15 Apr 2026 00:19:43 GMT</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNMU1HeGlqal9aWUNBTHM3bC1lb2ZsX01BVnZnd3Zjanhld2xhSWVSeHF3T0YtVGJEMHZDVlJaRkVKQm95b1VvdE1YVTVjbkxkZHN2azItQTU3SDZCeHRMUUhQSDBlVXRvWXlyYzlDQ3ExcXExM3hPb2N5VWZnTWs3Vldscw?oc=5</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="n">
-        <v>46127.01369212963</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Trump contro tutti, la Lega ripensa la piazza di sabato. Silvia Sardone a Open: «Ue folle sul Patto di Stabilità, sì alla remigrazione - Open</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Trump against everyone, the League rethinks the square on Saturday. Silvia Sardone at Open: «EU crazy about the Stability Pact, yes to remigration - Open</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:51:10 GMT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNUE1uakpyd3RWZDN4R1BuYkFRTG55R1RsSXRLZ3ZoVW9DZHA4MnBYTHNHQVZnemZXeV9fUmoxUk5pR1oyQkpJczZ6dU1tQmtKMXVEZU1ONzdaM3hBZW1WVFdlNlUwai1rbVVjcGNKX1gwRWRURUdJQW0wbzJPVDNJd05RY3ZfODVEYWVjbE82NXZuZ0lzSFhwMjJrek1KUld1SGFGTk5XcXhQUE5RQ3c?oc=5</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="n">
-        <v>46126.74386574074</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Hate Crime Europe English</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Reform activist suspended over racist and antisemitic comments remains election agent - The Guardian</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Reform activist suspended over racist and antisemitic comments remains election agent - The Guardian</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 19:22:00 GMT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQUnVkRVNPU0hwZ0FDdGNDQUZralNUX28wZ0RUWG15Q1ozZGpzRmVqYkViNjRteHI1MVFlOWMxTEpYSWVnek9qWlNmeGFKb0ZWeFIwaWZFdEs4dlR4WDFiSzk2TnNHS3Iyd0tyZjI0dklmOEQtV2N5UkVYMldUaWdWVXZzVHFtc0dBaWRUVGxOQVRaLVVnazhvTUZCd0hBZEFlMWNGVmJsMFhCa01kQWt6RGU2ZlBnX2J4NXU5WW83QzlPWUozTll6dHprTUJJZHpNRGF0RC1jVzZFQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="n">
-        <v>46126.80694444444</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Hate Crime Europe English</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>French minister seeks to ban Kanye West concert in Marseille over antisemitic remarks - Le Monde.fr</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>French minister seeks to ban Kanye West concert in Marseille over antisemitic remarks - Le Monde.fr</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 11:47:33 GMT</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOWmFhbDh3Vlo0Skh5VXZPZWtvcS15c2tKTGhSZUZmQU1zVmRtLXhMN05mWHFPdVIweTI1a0stZFdyd2VlWWl6U2FtM3dpdFVuVXZNQVl2cEpFRlF6dWRUdk9EcW0tWHl1S3ljejl0MjN6NnhLNFJTYWljR19SNEdicDNLb2lIaU5JUklMYXJ1dGRHUHI5TGUzZ2tQWVI3TjRrQzlBTHo5XzlDeDdIa2hkcHpRa1NpazdkMUpCaGdmcmtwY2lpWmw0dUJWSWdXMzNibXdKVk9JRDlJa0pUcTJXeUE0VWpmSTVqZU55X3BvUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="n">
-        <v>46126.49135416667</v>
+        <v>46127.41574074074</v>
       </c>
     </row>
   </sheetData>
